--- a/table_adjust.xlsx
+++ b/table_adjust.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8268aba086fcb9b8/KDA_Trinh Võ/KDA data/PYTHON_OPERATION/ma_shondo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="8_{753EE1B0-0A9A-452A-BCE9-F8BF0F505AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5912E2B9-17FC-49EA-9511-7B5001373ECC}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{753EE1B0-0A9A-452A-BCE9-F8BF0F505AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7FFA8E9-E670-47B9-9EDB-D7F92FA7EDFE}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F1D8C3B-B510-45F3-82FB-DF857C4D318C}"/>
   </bookViews>
   <sheets>
     <sheet name="kpi" sheetId="1" r:id="rId1"/>
-    <sheet name="type_products" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">kpi!$A$1:$F$320</definedName>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="40">
   <si>
     <t>KDC</t>
   </si>
@@ -154,252 +153,6 @@
   </si>
   <si>
     <t>year</t>
-  </si>
-  <si>
-    <t>SUK0009</t>
-  </si>
-  <si>
-    <t>SUK1010</t>
-  </si>
-  <si>
-    <t>SUK2222</t>
-  </si>
-  <si>
-    <t>F100020</t>
-  </si>
-  <si>
-    <t>F100025</t>
-  </si>
-  <si>
-    <t>F103031</t>
-  </si>
-  <si>
-    <t>F103939</t>
-  </si>
-  <si>
-    <t>F106969</t>
-  </si>
-  <si>
-    <t>F107979</t>
-  </si>
-  <si>
-    <t>F100009</t>
-  </si>
-  <si>
-    <t>SUK2020</t>
-  </si>
-  <si>
-    <t>SUK2525</t>
-  </si>
-  <si>
-    <t>SUK7070</t>
-  </si>
-  <si>
-    <t>SLI0970</t>
-  </si>
-  <si>
-    <t>SLI1060</t>
-  </si>
-  <si>
-    <t>SLI2060</t>
-  </si>
-  <si>
-    <t>SLI7071</t>
-  </si>
-  <si>
-    <t>DRE0101</t>
-  </si>
-  <si>
-    <t>DRE1010</t>
-  </si>
-  <si>
-    <t>DRE3535</t>
-  </si>
-  <si>
-    <t>DRE7070</t>
-  </si>
-  <si>
-    <t>DLI0160</t>
-  </si>
-  <si>
-    <t>DLI7070</t>
-  </si>
-  <si>
-    <t>DLI9050</t>
-  </si>
-  <si>
-    <t>F107090</t>
-  </si>
-  <si>
-    <t>GM20101</t>
-  </si>
-  <si>
-    <t>SN30101</t>
-  </si>
-  <si>
-    <t>SN31010</t>
-  </si>
-  <si>
-    <t>SN32525</t>
-  </si>
-  <si>
-    <t>F102222</t>
-  </si>
-  <si>
-    <t>F100000</t>
-  </si>
-  <si>
-    <t>F101010</t>
-  </si>
-  <si>
-    <t>F103030</t>
-  </si>
-  <si>
-    <t>F101011</t>
-  </si>
-  <si>
-    <t>F107079</t>
-  </si>
-  <si>
-    <t>DRE0909</t>
-  </si>
-  <si>
-    <t>DRE3030</t>
-  </si>
-  <si>
-    <t>DRE7171</t>
-  </si>
-  <si>
-    <t>SUK2424</t>
-  </si>
-  <si>
-    <t>SUK3535</t>
-  </si>
-  <si>
-    <t>SUK9595</t>
-  </si>
-  <si>
-    <t>FXK2020</t>
-  </si>
-  <si>
-    <t>FXK4040</t>
-  </si>
-  <si>
-    <t>SLI3030</t>
-  </si>
-  <si>
-    <t>SLI3535</t>
-  </si>
-  <si>
-    <t>SN37070</t>
-  </si>
-  <si>
-    <t>SN40010</t>
-  </si>
-  <si>
-    <t>SN41000</t>
-  </si>
-  <si>
-    <t>FXK3031</t>
-  </si>
-  <si>
-    <t>FXK3939</t>
-  </si>
-  <si>
-    <t>FXK6969</t>
-  </si>
-  <si>
-    <t>FXK7979</t>
-  </si>
-  <si>
-    <t>TR60909</t>
-  </si>
-  <si>
-    <t>TR62525</t>
-  </si>
-  <si>
-    <t>TR67070</t>
-  </si>
-  <si>
-    <t>TR69595</t>
-  </si>
-  <si>
-    <t>F107070</t>
-  </si>
-  <si>
-    <t>F105050</t>
-  </si>
-  <si>
-    <t>SUK7090</t>
-  </si>
-  <si>
-    <t>DEV1010</t>
-  </si>
-  <si>
-    <t>DTB2525</t>
-  </si>
-  <si>
-    <t>DTB9595</t>
-  </si>
-  <si>
-    <t>DTT9595</t>
-  </si>
-  <si>
-    <t>DRE0009</t>
-  </si>
-  <si>
-    <t>DRE2424</t>
-  </si>
-  <si>
-    <t>DRE7090</t>
-  </si>
-  <si>
-    <t>SLI9070</t>
-  </si>
-  <si>
-    <t>SU22424</t>
-  </si>
-  <si>
-    <t>SU23535</t>
-  </si>
-  <si>
-    <t>SU29595</t>
-  </si>
-  <si>
-    <t>LC31010</t>
-  </si>
-  <si>
-    <t>LC32020</t>
-  </si>
-  <si>
-    <t>LC37070</t>
-  </si>
-  <si>
-    <t>LC39090</t>
-  </si>
-  <si>
-    <t>LDR3030</t>
-  </si>
-  <si>
-    <t>LDR4040</t>
-  </si>
-  <si>
-    <t>LDR7070</t>
-  </si>
-  <si>
-    <t>SN42020</t>
-  </si>
-  <si>
-    <t>SN47171</t>
-  </si>
-  <si>
-    <t>default_code</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>Eva foam</t>
   </si>
   <si>
     <t>Date</t>
@@ -814,7 +567,7 @@
         <v>36</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>119</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -4830,7 +4583,7 @@
         <v>2</v>
       </c>
       <c r="B193" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="C193" s="1">
         <v>85948400</v>
@@ -4851,7 +4604,7 @@
         <v>2</v>
       </c>
       <c r="B194" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="C194" s="1">
         <v>61652750</v>
@@ -4872,7 +4625,7 @@
         <v>2</v>
       </c>
       <c r="B195" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="C195" s="1">
         <v>222559500</v>
@@ -4893,7 +4646,7 @@
         <v>2</v>
       </c>
       <c r="B196" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="C196">
         <v>156030000</v>
@@ -4914,7 +4667,7 @@
         <v>2</v>
       </c>
       <c r="B197" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="C197">
         <v>163625000</v>
@@ -4935,7 +4688,7 @@
         <v>2</v>
       </c>
       <c r="B198" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="C198">
         <v>163625000</v>
@@ -4956,7 +4709,7 @@
         <v>2</v>
       </c>
       <c r="B199" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="C199">
         <v>389600000</v>
@@ -4977,7 +4730,7 @@
         <v>2</v>
       </c>
       <c r="B200" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="C200">
         <v>467550000</v>
@@ -4998,7 +4751,7 @@
         <v>2</v>
       </c>
       <c r="B201" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="C201">
         <v>259750000</v>
@@ -5019,7 +4772,7 @@
         <v>2</v>
       </c>
       <c r="B202" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="C202" s="1">
         <v>109003800</v>
@@ -5040,7 +4793,7 @@
         <v>2</v>
       </c>
       <c r="B203" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="C203" s="1">
         <v>43255250</v>
@@ -5061,7 +4814,7 @@
         <v>2</v>
       </c>
       <c r="B204" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="C204" s="1">
         <v>67192300</v>
@@ -5082,7 +4835,7 @@
         <v>2</v>
       </c>
       <c r="B205" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="C205">
         <v>222900000</v>
@@ -5103,7 +4856,7 @@
         <v>2</v>
       </c>
       <c r="B206" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="C206">
         <v>233750000</v>
@@ -5124,7 +4877,7 @@
         <v>2</v>
       </c>
       <c r="B207" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="C207">
         <v>233750000</v>
@@ -5145,7 +4898,7 @@
         <v>2</v>
       </c>
       <c r="B208" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="C208">
         <v>623360000</v>
@@ -5166,7 +4919,7 @@
         <v>2</v>
       </c>
       <c r="B209" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="C209">
         <v>748080000</v>
@@ -5187,7 +4940,7 @@
         <v>2</v>
       </c>
       <c r="B210" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="C210">
         <v>415600000</v>
@@ -6999,7 +6752,7 @@
         <v>2</v>
       </c>
       <c r="B298" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="C298">
         <v>150000000</v>
@@ -7020,7 +6773,7 @@
         <v>2</v>
       </c>
       <c r="B299" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="C299">
         <v>100000000</v>
@@ -7041,7 +6794,7 @@
         <v>2</v>
       </c>
       <c r="B300" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="C300">
         <v>170000000</v>
@@ -7062,7 +6815,7 @@
         <v>2</v>
       </c>
       <c r="B301" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="C301">
         <v>75000000</v>
@@ -7083,7 +6836,7 @@
         <v>2</v>
       </c>
       <c r="B302" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="C302">
         <v>100000000</v>
@@ -7104,7 +6857,7 @@
         <v>2</v>
       </c>
       <c r="B303" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="C303">
         <v>85000000</v>
@@ -7480,658 +7233,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A5C64FF-69A1-459B-B725-147E81431F3A}">
-  <dimension ref="A1:B80"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>58</v>
-      </c>
-      <c r="B23" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>60</v>
-      </c>
-      <c r="B25" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>61</v>
-      </c>
-      <c r="B26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>62</v>
-      </c>
-      <c r="B27" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>65</v>
-      </c>
-      <c r="B30" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>66</v>
-      </c>
-      <c r="B31" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>67</v>
-      </c>
-      <c r="B32" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>68</v>
-      </c>
-      <c r="B33" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>69</v>
-      </c>
-      <c r="B34" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>70</v>
-      </c>
-      <c r="B35" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>73</v>
-      </c>
-      <c r="B38" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>74</v>
-      </c>
-      <c r="B39" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>75</v>
-      </c>
-      <c r="B40" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>76</v>
-      </c>
-      <c r="B41" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>77</v>
-      </c>
-      <c r="B42" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>78</v>
-      </c>
-      <c r="B43" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>79</v>
-      </c>
-      <c r="B44" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>80</v>
-      </c>
-      <c r="B45" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>81</v>
-      </c>
-      <c r="B46" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>82</v>
-      </c>
-      <c r="B47" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>83</v>
-      </c>
-      <c r="B48" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>84</v>
-      </c>
-      <c r="B49" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>85</v>
-      </c>
-      <c r="B50" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>86</v>
-      </c>
-      <c r="B51" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>87</v>
-      </c>
-      <c r="B52" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>88</v>
-      </c>
-      <c r="B53" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>89</v>
-      </c>
-      <c r="B54" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>90</v>
-      </c>
-      <c r="B55" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>91</v>
-      </c>
-      <c r="B56" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>92</v>
-      </c>
-      <c r="B57" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>93</v>
-      </c>
-      <c r="B58" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>94</v>
-      </c>
-      <c r="B59" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>95</v>
-      </c>
-      <c r="B60" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>96</v>
-      </c>
-      <c r="B61" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>97</v>
-      </c>
-      <c r="B62" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>98</v>
-      </c>
-      <c r="B63" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>99</v>
-      </c>
-      <c r="B64" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>100</v>
-      </c>
-      <c r="B65" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>101</v>
-      </c>
-      <c r="B66" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>102</v>
-      </c>
-      <c r="B67" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>103</v>
-      </c>
-      <c r="B68" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>104</v>
-      </c>
-      <c r="B69" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>105</v>
-      </c>
-      <c r="B70" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>106</v>
-      </c>
-      <c r="B71" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>107</v>
-      </c>
-      <c r="B72" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>108</v>
-      </c>
-      <c r="B73" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>109</v>
-      </c>
-      <c r="B74" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>110</v>
-      </c>
-      <c r="B75" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>111</v>
-      </c>
-      <c r="B76" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>112</v>
-      </c>
-      <c r="B77" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>113</v>
-      </c>
-      <c r="B78" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>114</v>
-      </c>
-      <c r="B79" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>115</v>
-      </c>
-      <c r="B80" t="s">
-        <v>118</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/table_adjust.xlsx
+++ b/table_adjust.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8268aba086fcb9b8/KDA_Trinh Võ/KDA data/PYTHON_OPERATION/ma_shondo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{753EE1B0-0A9A-452A-BCE9-F8BF0F505AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7FFA8E9-E670-47B9-9EDB-D7F92FA7EDFE}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="8_{753EE1B0-0A9A-452A-BCE9-F8BF0F505AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{293CD153-6603-462B-B137-55CAC8FB3D2E}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F1D8C3B-B510-45F3-82FB-DF857C4D318C}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="kpi" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">kpi!$A$1:$F$320</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">kpi!$A$1:$F$595</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="47">
   <si>
     <t>KDC</t>
   </si>
@@ -162,6 +162,27 @@
   </si>
   <si>
     <t>FB/INS/ZL/NB</t>
+  </si>
+  <si>
+    <t>101AEONHP</t>
+  </si>
+  <si>
+    <t>CH (thay BD)</t>
+  </si>
+  <si>
+    <t>CH MỚI 1</t>
+  </si>
+  <si>
+    <t>CH MỚI 2</t>
+  </si>
+  <si>
+    <t>CH MỚI 3</t>
+  </si>
+  <si>
+    <t>CH MỚI 4</t>
+  </si>
+  <si>
+    <t>CH MỚI 5</t>
   </si>
 </sst>
 </file>
@@ -542,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CECFDCC4-BC95-4EB9-8D2E-CA772917AEFE}">
-  <dimension ref="A1:F320"/>
+  <dimension ref="A1:F595"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="20.08203125" bestFit="1" customWidth="1"/>
@@ -6470,7 +6491,7 @@
         <v>2025</v>
       </c>
       <c r="F284" s="3">
-        <f t="shared" ref="F284:F320" si="6">DATE(E284,D284,1)</f>
+        <f t="shared" ref="F284:F347" si="6">DATE(E284,D284,1)</f>
         <v>45992</v>
       </c>
     </row>
@@ -7228,6 +7249,5781 @@
       <c r="F320" s="3">
         <f t="shared" si="6"/>
         <v>45992</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>2</v>
+      </c>
+      <c r="B321" t="s">
+        <v>28</v>
+      </c>
+      <c r="C321">
+        <v>3125000000</v>
+      </c>
+      <c r="D321" s="4">
+        <v>1</v>
+      </c>
+      <c r="E321">
+        <v>2026</v>
+      </c>
+      <c r="F321" s="3">
+        <f t="shared" si="6"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>2</v>
+      </c>
+      <c r="B322" t="s">
+        <v>28</v>
+      </c>
+      <c r="C322">
+        <v>2187500000</v>
+      </c>
+      <c r="D322" s="4">
+        <v>2</v>
+      </c>
+      <c r="E322">
+        <v>2026</v>
+      </c>
+      <c r="F322" s="3">
+        <f t="shared" si="6"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>2</v>
+      </c>
+      <c r="B323" t="s">
+        <v>28</v>
+      </c>
+      <c r="C323">
+        <v>3125000000</v>
+      </c>
+      <c r="D323" s="4">
+        <v>3</v>
+      </c>
+      <c r="E323">
+        <v>2026</v>
+      </c>
+      <c r="F323" s="3">
+        <f t="shared" si="6"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>2</v>
+      </c>
+      <c r="B324" t="s">
+        <v>28</v>
+      </c>
+      <c r="C324">
+        <v>2812500000</v>
+      </c>
+      <c r="D324" s="4">
+        <v>4</v>
+      </c>
+      <c r="E324">
+        <v>2026</v>
+      </c>
+      <c r="F324" s="3">
+        <f t="shared" si="6"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>2</v>
+      </c>
+      <c r="B325" t="s">
+        <v>28</v>
+      </c>
+      <c r="C325">
+        <v>3125000000</v>
+      </c>
+      <c r="D325" s="4">
+        <v>5</v>
+      </c>
+      <c r="E325">
+        <v>2026</v>
+      </c>
+      <c r="F325" s="3">
+        <f t="shared" si="6"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>2</v>
+      </c>
+      <c r="B326" t="s">
+        <v>28</v>
+      </c>
+      <c r="C326">
+        <v>3125000000</v>
+      </c>
+      <c r="D326" s="4">
+        <v>6</v>
+      </c>
+      <c r="E326">
+        <v>2026</v>
+      </c>
+      <c r="F326" s="3">
+        <f t="shared" si="6"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
+        <v>2</v>
+      </c>
+      <c r="B327" t="s">
+        <v>28</v>
+      </c>
+      <c r="C327">
+        <v>5000000000</v>
+      </c>
+      <c r="D327" s="4">
+        <v>7</v>
+      </c>
+      <c r="E327">
+        <v>2026</v>
+      </c>
+      <c r="F327" s="3">
+        <f t="shared" si="6"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A328" t="s">
+        <v>2</v>
+      </c>
+      <c r="B328" t="s">
+        <v>28</v>
+      </c>
+      <c r="C328">
+        <v>8125000000</v>
+      </c>
+      <c r="D328" s="4">
+        <v>8</v>
+      </c>
+      <c r="E328">
+        <v>2026</v>
+      </c>
+      <c r="F328" s="3">
+        <f t="shared" si="6"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
+        <v>2</v>
+      </c>
+      <c r="B329" t="s">
+        <v>28</v>
+      </c>
+      <c r="C329">
+        <v>5000000000</v>
+      </c>
+      <c r="D329" s="4">
+        <v>9</v>
+      </c>
+      <c r="E329">
+        <v>2026</v>
+      </c>
+      <c r="F329" s="3">
+        <f t="shared" si="6"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A330" t="s">
+        <v>2</v>
+      </c>
+      <c r="B330" t="s">
+        <v>28</v>
+      </c>
+      <c r="C330">
+        <v>4375000000</v>
+      </c>
+      <c r="D330" s="4">
+        <v>10</v>
+      </c>
+      <c r="E330">
+        <v>2026</v>
+      </c>
+      <c r="F330" s="3">
+        <f t="shared" si="6"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A331" t="s">
+        <v>2</v>
+      </c>
+      <c r="B331" t="s">
+        <v>28</v>
+      </c>
+      <c r="C331">
+        <v>5625000000</v>
+      </c>
+      <c r="D331" s="4">
+        <v>11</v>
+      </c>
+      <c r="E331">
+        <v>2026</v>
+      </c>
+      <c r="F331" s="3">
+        <f t="shared" si="6"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>2</v>
+      </c>
+      <c r="B332" t="s">
+        <v>28</v>
+      </c>
+      <c r="C332">
+        <v>4375000000</v>
+      </c>
+      <c r="D332" s="4">
+        <v>12</v>
+      </c>
+      <c r="E332">
+        <v>2026</v>
+      </c>
+      <c r="F332" s="3">
+        <f t="shared" si="6"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>2</v>
+      </c>
+      <c r="B333" t="s">
+        <v>29</v>
+      </c>
+      <c r="C333">
+        <v>1750000000</v>
+      </c>
+      <c r="D333" s="4">
+        <v>1</v>
+      </c>
+      <c r="E333">
+        <v>2026</v>
+      </c>
+      <c r="F333" s="3">
+        <f t="shared" si="6"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>2</v>
+      </c>
+      <c r="B334" t="s">
+        <v>29</v>
+      </c>
+      <c r="C334">
+        <v>1225000000</v>
+      </c>
+      <c r="D334" s="4">
+        <v>2</v>
+      </c>
+      <c r="E334">
+        <v>2026</v>
+      </c>
+      <c r="F334" s="3">
+        <f t="shared" si="6"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>2</v>
+      </c>
+      <c r="B335" t="s">
+        <v>29</v>
+      </c>
+      <c r="C335">
+        <v>1750000000</v>
+      </c>
+      <c r="D335" s="4">
+        <v>3</v>
+      </c>
+      <c r="E335">
+        <v>2026</v>
+      </c>
+      <c r="F335" s="3">
+        <f t="shared" si="6"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>2</v>
+      </c>
+      <c r="B336" t="s">
+        <v>29</v>
+      </c>
+      <c r="C336">
+        <v>1575000000</v>
+      </c>
+      <c r="D336" s="4">
+        <v>4</v>
+      </c>
+      <c r="E336">
+        <v>2026</v>
+      </c>
+      <c r="F336" s="3">
+        <f t="shared" si="6"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A337" t="s">
+        <v>2</v>
+      </c>
+      <c r="B337" t="s">
+        <v>29</v>
+      </c>
+      <c r="C337">
+        <v>1750000000</v>
+      </c>
+      <c r="D337" s="4">
+        <v>5</v>
+      </c>
+      <c r="E337">
+        <v>2026</v>
+      </c>
+      <c r="F337" s="3">
+        <f t="shared" si="6"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A338" t="s">
+        <v>2</v>
+      </c>
+      <c r="B338" t="s">
+        <v>29</v>
+      </c>
+      <c r="C338">
+        <v>1750000000</v>
+      </c>
+      <c r="D338" s="4">
+        <v>6</v>
+      </c>
+      <c r="E338">
+        <v>2026</v>
+      </c>
+      <c r="F338" s="3">
+        <f t="shared" si="6"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A339" t="s">
+        <v>2</v>
+      </c>
+      <c r="B339" t="s">
+        <v>29</v>
+      </c>
+      <c r="C339">
+        <v>2800000000</v>
+      </c>
+      <c r="D339" s="4">
+        <v>7</v>
+      </c>
+      <c r="E339">
+        <v>2026</v>
+      </c>
+      <c r="F339" s="3">
+        <f t="shared" si="6"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A340" t="s">
+        <v>2</v>
+      </c>
+      <c r="B340" t="s">
+        <v>29</v>
+      </c>
+      <c r="C340">
+        <v>4550000000</v>
+      </c>
+      <c r="D340" s="4">
+        <v>8</v>
+      </c>
+      <c r="E340">
+        <v>2026</v>
+      </c>
+      <c r="F340" s="3">
+        <f t="shared" si="6"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>2</v>
+      </c>
+      <c r="B341" t="s">
+        <v>29</v>
+      </c>
+      <c r="C341">
+        <v>2800000000</v>
+      </c>
+      <c r="D341" s="4">
+        <v>9</v>
+      </c>
+      <c r="E341">
+        <v>2026</v>
+      </c>
+      <c r="F341" s="3">
+        <f t="shared" si="6"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A342" t="s">
+        <v>2</v>
+      </c>
+      <c r="B342" t="s">
+        <v>29</v>
+      </c>
+      <c r="C342">
+        <v>2450000000</v>
+      </c>
+      <c r="D342" s="4">
+        <v>10</v>
+      </c>
+      <c r="E342">
+        <v>2026</v>
+      </c>
+      <c r="F342" s="3">
+        <f t="shared" si="6"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A343" t="s">
+        <v>2</v>
+      </c>
+      <c r="B343" t="s">
+        <v>29</v>
+      </c>
+      <c r="C343">
+        <v>3150000000</v>
+      </c>
+      <c r="D343" s="4">
+        <v>11</v>
+      </c>
+      <c r="E343">
+        <v>2026</v>
+      </c>
+      <c r="F343" s="3">
+        <f t="shared" si="6"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A344" t="s">
+        <v>2</v>
+      </c>
+      <c r="B344" t="s">
+        <v>29</v>
+      </c>
+      <c r="C344">
+        <v>2450000000</v>
+      </c>
+      <c r="D344" s="4">
+        <v>12</v>
+      </c>
+      <c r="E344">
+        <v>2026</v>
+      </c>
+      <c r="F344" s="3">
+        <f t="shared" si="6"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A345" t="s">
+        <v>2</v>
+      </c>
+      <c r="B345" t="s">
+        <v>38</v>
+      </c>
+      <c r="C345">
+        <v>75000000</v>
+      </c>
+      <c r="D345" s="4">
+        <v>1</v>
+      </c>
+      <c r="E345">
+        <v>2026</v>
+      </c>
+      <c r="F345" s="3">
+        <f t="shared" si="6"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A346" t="s">
+        <v>2</v>
+      </c>
+      <c r="B346" t="s">
+        <v>38</v>
+      </c>
+      <c r="C346">
+        <v>52500000</v>
+      </c>
+      <c r="D346" s="4">
+        <v>2</v>
+      </c>
+      <c r="E346">
+        <v>2026</v>
+      </c>
+      <c r="F346" s="3">
+        <f t="shared" si="6"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A347" t="s">
+        <v>2</v>
+      </c>
+      <c r="B347" t="s">
+        <v>38</v>
+      </c>
+      <c r="C347">
+        <v>75000000</v>
+      </c>
+      <c r="D347" s="4">
+        <v>3</v>
+      </c>
+      <c r="E347">
+        <v>2026</v>
+      </c>
+      <c r="F347" s="3">
+        <f t="shared" si="6"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>2</v>
+      </c>
+      <c r="B348" t="s">
+        <v>38</v>
+      </c>
+      <c r="C348">
+        <v>67500000</v>
+      </c>
+      <c r="D348" s="4">
+        <v>4</v>
+      </c>
+      <c r="E348">
+        <v>2026</v>
+      </c>
+      <c r="F348" s="3">
+        <f t="shared" ref="F348:F411" si="7">DATE(E348,D348,1)</f>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>2</v>
+      </c>
+      <c r="B349" t="s">
+        <v>38</v>
+      </c>
+      <c r="C349">
+        <v>75000000</v>
+      </c>
+      <c r="D349" s="4">
+        <v>5</v>
+      </c>
+      <c r="E349">
+        <v>2026</v>
+      </c>
+      <c r="F349" s="3">
+        <f t="shared" si="7"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A350" t="s">
+        <v>2</v>
+      </c>
+      <c r="B350" t="s">
+        <v>38</v>
+      </c>
+      <c r="C350">
+        <v>75000000</v>
+      </c>
+      <c r="D350" s="4">
+        <v>6</v>
+      </c>
+      <c r="E350">
+        <v>2026</v>
+      </c>
+      <c r="F350" s="3">
+        <f t="shared" si="7"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A351" t="s">
+        <v>2</v>
+      </c>
+      <c r="B351" t="s">
+        <v>38</v>
+      </c>
+      <c r="C351">
+        <v>120000000</v>
+      </c>
+      <c r="D351" s="4">
+        <v>7</v>
+      </c>
+      <c r="E351">
+        <v>2026</v>
+      </c>
+      <c r="F351" s="3">
+        <f t="shared" si="7"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A352" t="s">
+        <v>2</v>
+      </c>
+      <c r="B352" t="s">
+        <v>38</v>
+      </c>
+      <c r="C352">
+        <v>195000000</v>
+      </c>
+      <c r="D352" s="4">
+        <v>8</v>
+      </c>
+      <c r="E352">
+        <v>2026</v>
+      </c>
+      <c r="F352" s="3">
+        <f t="shared" si="7"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A353" t="s">
+        <v>2</v>
+      </c>
+      <c r="B353" t="s">
+        <v>38</v>
+      </c>
+      <c r="C353">
+        <v>120000000</v>
+      </c>
+      <c r="D353" s="4">
+        <v>9</v>
+      </c>
+      <c r="E353">
+        <v>2026</v>
+      </c>
+      <c r="F353" s="3">
+        <f t="shared" si="7"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A354" t="s">
+        <v>2</v>
+      </c>
+      <c r="B354" t="s">
+        <v>38</v>
+      </c>
+      <c r="C354">
+        <v>105000000</v>
+      </c>
+      <c r="D354" s="4">
+        <v>10</v>
+      </c>
+      <c r="E354">
+        <v>2026</v>
+      </c>
+      <c r="F354" s="3">
+        <f t="shared" si="7"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A355" t="s">
+        <v>2</v>
+      </c>
+      <c r="B355" t="s">
+        <v>38</v>
+      </c>
+      <c r="C355">
+        <v>135000000</v>
+      </c>
+      <c r="D355" s="4">
+        <v>11</v>
+      </c>
+      <c r="E355">
+        <v>2026</v>
+      </c>
+      <c r="F355" s="3">
+        <f t="shared" si="7"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A356" t="s">
+        <v>2</v>
+      </c>
+      <c r="B356" t="s">
+        <v>38</v>
+      </c>
+      <c r="C356">
+        <v>105000000</v>
+      </c>
+      <c r="D356" s="4">
+        <v>12</v>
+      </c>
+      <c r="E356">
+        <v>2026</v>
+      </c>
+      <c r="F356" s="3">
+        <f t="shared" si="7"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A357" t="s">
+        <v>2</v>
+      </c>
+      <c r="B357" t="s">
+        <v>39</v>
+      </c>
+      <c r="C357">
+        <v>50000000</v>
+      </c>
+      <c r="D357" s="4">
+        <v>1</v>
+      </c>
+      <c r="E357">
+        <v>2026</v>
+      </c>
+      <c r="F357" s="3">
+        <f t="shared" si="7"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A358" t="s">
+        <v>2</v>
+      </c>
+      <c r="B358" t="s">
+        <v>39</v>
+      </c>
+      <c r="C358">
+        <v>35000000</v>
+      </c>
+      <c r="D358" s="4">
+        <v>2</v>
+      </c>
+      <c r="E358">
+        <v>2026</v>
+      </c>
+      <c r="F358" s="3">
+        <f t="shared" si="7"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A359" t="s">
+        <v>2</v>
+      </c>
+      <c r="B359" t="s">
+        <v>39</v>
+      </c>
+      <c r="C359">
+        <v>50000000</v>
+      </c>
+      <c r="D359" s="4">
+        <v>3</v>
+      </c>
+      <c r="E359">
+        <v>2026</v>
+      </c>
+      <c r="F359" s="3">
+        <f t="shared" si="7"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A360" t="s">
+        <v>2</v>
+      </c>
+      <c r="B360" t="s">
+        <v>39</v>
+      </c>
+      <c r="C360">
+        <v>45000000</v>
+      </c>
+      <c r="D360" s="4">
+        <v>4</v>
+      </c>
+      <c r="E360">
+        <v>2026</v>
+      </c>
+      <c r="F360" s="3">
+        <f t="shared" si="7"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A361" t="s">
+        <v>2</v>
+      </c>
+      <c r="B361" t="s">
+        <v>39</v>
+      </c>
+      <c r="C361">
+        <v>50000000</v>
+      </c>
+      <c r="D361" s="4">
+        <v>5</v>
+      </c>
+      <c r="E361">
+        <v>2026</v>
+      </c>
+      <c r="F361" s="3">
+        <f t="shared" si="7"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A362" t="s">
+        <v>2</v>
+      </c>
+      <c r="B362" t="s">
+        <v>39</v>
+      </c>
+      <c r="C362">
+        <v>50000000</v>
+      </c>
+      <c r="D362" s="4">
+        <v>6</v>
+      </c>
+      <c r="E362">
+        <v>2026</v>
+      </c>
+      <c r="F362" s="3">
+        <f t="shared" si="7"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A363" t="s">
+        <v>2</v>
+      </c>
+      <c r="B363" t="s">
+        <v>39</v>
+      </c>
+      <c r="C363">
+        <v>80000000</v>
+      </c>
+      <c r="D363" s="4">
+        <v>7</v>
+      </c>
+      <c r="E363">
+        <v>2026</v>
+      </c>
+      <c r="F363" s="3">
+        <f t="shared" si="7"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A364" t="s">
+        <v>2</v>
+      </c>
+      <c r="B364" t="s">
+        <v>39</v>
+      </c>
+      <c r="C364">
+        <v>130000000</v>
+      </c>
+      <c r="D364" s="4">
+        <v>8</v>
+      </c>
+      <c r="E364">
+        <v>2026</v>
+      </c>
+      <c r="F364" s="3">
+        <f t="shared" si="7"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A365" t="s">
+        <v>2</v>
+      </c>
+      <c r="B365" t="s">
+        <v>39</v>
+      </c>
+      <c r="C365">
+        <v>80000000</v>
+      </c>
+      <c r="D365" s="4">
+        <v>9</v>
+      </c>
+      <c r="E365">
+        <v>2026</v>
+      </c>
+      <c r="F365" s="3">
+        <f t="shared" si="7"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A366" t="s">
+        <v>2</v>
+      </c>
+      <c r="B366" t="s">
+        <v>39</v>
+      </c>
+      <c r="C366">
+        <v>70000000</v>
+      </c>
+      <c r="D366" s="4">
+        <v>10</v>
+      </c>
+      <c r="E366">
+        <v>2026</v>
+      </c>
+      <c r="F366" s="3">
+        <f t="shared" si="7"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A367" t="s">
+        <v>2</v>
+      </c>
+      <c r="B367" t="s">
+        <v>39</v>
+      </c>
+      <c r="C367">
+        <v>90000000</v>
+      </c>
+      <c r="D367" s="4">
+        <v>11</v>
+      </c>
+      <c r="E367">
+        <v>2026</v>
+      </c>
+      <c r="F367" s="3">
+        <f t="shared" si="7"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A368" t="s">
+        <v>2</v>
+      </c>
+      <c r="B368" t="s">
+        <v>39</v>
+      </c>
+      <c r="C368">
+        <v>70000000</v>
+      </c>
+      <c r="D368" s="4">
+        <v>12</v>
+      </c>
+      <c r="E368">
+        <v>2026</v>
+      </c>
+      <c r="F368" s="3">
+        <f t="shared" si="7"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A369" t="s">
+        <v>0</v>
+      </c>
+      <c r="B369" t="s">
+        <v>9</v>
+      </c>
+      <c r="C369">
+        <v>320000000</v>
+      </c>
+      <c r="D369" s="4">
+        <v>1</v>
+      </c>
+      <c r="E369">
+        <v>2026</v>
+      </c>
+      <c r="F369" s="3">
+        <f t="shared" si="7"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A370" t="s">
+        <v>0</v>
+      </c>
+      <c r="B370" t="s">
+        <v>9</v>
+      </c>
+      <c r="C370">
+        <v>280000000</v>
+      </c>
+      <c r="D370" s="4">
+        <v>2</v>
+      </c>
+      <c r="E370">
+        <v>2026</v>
+      </c>
+      <c r="F370" s="3">
+        <f t="shared" si="7"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A371" t="s">
+        <v>0</v>
+      </c>
+      <c r="B371" t="s">
+        <v>9</v>
+      </c>
+      <c r="C371">
+        <v>240000000</v>
+      </c>
+      <c r="D371" s="4">
+        <v>3</v>
+      </c>
+      <c r="E371">
+        <v>2026</v>
+      </c>
+      <c r="F371" s="3">
+        <f t="shared" si="7"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A372" t="s">
+        <v>0</v>
+      </c>
+      <c r="B372" t="s">
+        <v>9</v>
+      </c>
+      <c r="C372">
+        <v>245000000</v>
+      </c>
+      <c r="D372" s="4">
+        <v>4</v>
+      </c>
+      <c r="E372">
+        <v>2026</v>
+      </c>
+      <c r="F372" s="3">
+        <f t="shared" si="7"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A373" t="s">
+        <v>0</v>
+      </c>
+      <c r="B373" t="s">
+        <v>9</v>
+      </c>
+      <c r="C373">
+        <v>250000000</v>
+      </c>
+      <c r="D373" s="4">
+        <v>5</v>
+      </c>
+      <c r="E373">
+        <v>2026</v>
+      </c>
+      <c r="F373" s="3">
+        <f t="shared" si="7"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A374" t="s">
+        <v>0</v>
+      </c>
+      <c r="B374" t="s">
+        <v>9</v>
+      </c>
+      <c r="C374">
+        <v>230000000</v>
+      </c>
+      <c r="D374" s="4">
+        <v>6</v>
+      </c>
+      <c r="E374">
+        <v>2026</v>
+      </c>
+      <c r="F374" s="3">
+        <f t="shared" si="7"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A375" t="s">
+        <v>0</v>
+      </c>
+      <c r="B375" t="s">
+        <v>9</v>
+      </c>
+      <c r="C375">
+        <v>290000000</v>
+      </c>
+      <c r="D375" s="4">
+        <v>7</v>
+      </c>
+      <c r="E375">
+        <v>2026</v>
+      </c>
+      <c r="F375" s="3">
+        <f t="shared" si="7"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A376" t="s">
+        <v>0</v>
+      </c>
+      <c r="B376" t="s">
+        <v>9</v>
+      </c>
+      <c r="C376">
+        <v>560000000</v>
+      </c>
+      <c r="D376" s="4">
+        <v>8</v>
+      </c>
+      <c r="E376">
+        <v>2026</v>
+      </c>
+      <c r="F376" s="3">
+        <f t="shared" si="7"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A377" t="s">
+        <v>0</v>
+      </c>
+      <c r="B377" t="s">
+        <v>9</v>
+      </c>
+      <c r="C377">
+        <v>260000000</v>
+      </c>
+      <c r="D377" s="4">
+        <v>9</v>
+      </c>
+      <c r="E377">
+        <v>2026</v>
+      </c>
+      <c r="F377" s="3">
+        <f t="shared" si="7"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A378" t="s">
+        <v>0</v>
+      </c>
+      <c r="B378" t="s">
+        <v>9</v>
+      </c>
+      <c r="C378">
+        <v>200000000</v>
+      </c>
+      <c r="D378" s="4">
+        <v>10</v>
+      </c>
+      <c r="E378">
+        <v>2026</v>
+      </c>
+      <c r="F378" s="3">
+        <f t="shared" si="7"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A379" t="s">
+        <v>0</v>
+      </c>
+      <c r="B379" t="s">
+        <v>9</v>
+      </c>
+      <c r="C379">
+        <v>330000000</v>
+      </c>
+      <c r="D379" s="4">
+        <v>11</v>
+      </c>
+      <c r="E379">
+        <v>2026</v>
+      </c>
+      <c r="F379" s="3">
+        <f t="shared" si="7"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A380" t="s">
+        <v>0</v>
+      </c>
+      <c r="B380" t="s">
+        <v>9</v>
+      </c>
+      <c r="C380">
+        <v>210000000</v>
+      </c>
+      <c r="D380" s="4">
+        <v>12</v>
+      </c>
+      <c r="E380">
+        <v>2026</v>
+      </c>
+      <c r="F380" s="3">
+        <f t="shared" si="7"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A381" t="s">
+        <v>0</v>
+      </c>
+      <c r="B381" t="s">
+        <v>10</v>
+      </c>
+      <c r="C381">
+        <v>250000000</v>
+      </c>
+      <c r="D381" s="4">
+        <v>1</v>
+      </c>
+      <c r="E381">
+        <v>2026</v>
+      </c>
+      <c r="F381" s="3">
+        <f t="shared" si="7"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A382" t="s">
+        <v>0</v>
+      </c>
+      <c r="B382" t="s">
+        <v>10</v>
+      </c>
+      <c r="C382">
+        <v>250000000</v>
+      </c>
+      <c r="D382" s="4">
+        <v>2</v>
+      </c>
+      <c r="E382">
+        <v>2026</v>
+      </c>
+      <c r="F382" s="3">
+        <f t="shared" si="7"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A383" t="s">
+        <v>0</v>
+      </c>
+      <c r="B383" t="s">
+        <v>10</v>
+      </c>
+      <c r="C383">
+        <v>210000000</v>
+      </c>
+      <c r="D383" s="4">
+        <v>3</v>
+      </c>
+      <c r="E383">
+        <v>2026</v>
+      </c>
+      <c r="F383" s="3">
+        <f t="shared" si="7"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A384" t="s">
+        <v>0</v>
+      </c>
+      <c r="B384" t="s">
+        <v>10</v>
+      </c>
+      <c r="C384">
+        <v>215000000</v>
+      </c>
+      <c r="D384" s="4">
+        <v>4</v>
+      </c>
+      <c r="E384">
+        <v>2026</v>
+      </c>
+      <c r="F384" s="3">
+        <f t="shared" si="7"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A385" t="s">
+        <v>0</v>
+      </c>
+      <c r="B385" t="s">
+        <v>10</v>
+      </c>
+      <c r="C385">
+        <v>220000000</v>
+      </c>
+      <c r="D385" s="4">
+        <v>5</v>
+      </c>
+      <c r="E385">
+        <v>2026</v>
+      </c>
+      <c r="F385" s="3">
+        <f t="shared" si="7"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A386" t="s">
+        <v>0</v>
+      </c>
+      <c r="B386" t="s">
+        <v>10</v>
+      </c>
+      <c r="C386">
+        <v>220000000</v>
+      </c>
+      <c r="D386" s="4">
+        <v>6</v>
+      </c>
+      <c r="E386">
+        <v>2026</v>
+      </c>
+      <c r="F386" s="3">
+        <f t="shared" si="7"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A387" t="s">
+        <v>0</v>
+      </c>
+      <c r="B387" t="s">
+        <v>10</v>
+      </c>
+      <c r="C387">
+        <v>270000000</v>
+      </c>
+      <c r="D387" s="4">
+        <v>7</v>
+      </c>
+      <c r="E387">
+        <v>2026</v>
+      </c>
+      <c r="F387" s="3">
+        <f t="shared" si="7"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A388" t="s">
+        <v>0</v>
+      </c>
+      <c r="B388" t="s">
+        <v>10</v>
+      </c>
+      <c r="C388">
+        <v>420000000</v>
+      </c>
+      <c r="D388" s="4">
+        <v>8</v>
+      </c>
+      <c r="E388">
+        <v>2026</v>
+      </c>
+      <c r="F388" s="3">
+        <f t="shared" si="7"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A389" t="s">
+        <v>0</v>
+      </c>
+      <c r="B389" t="s">
+        <v>10</v>
+      </c>
+      <c r="C389">
+        <v>240000000</v>
+      </c>
+      <c r="D389" s="4">
+        <v>9</v>
+      </c>
+      <c r="E389">
+        <v>2026</v>
+      </c>
+      <c r="F389" s="3">
+        <f t="shared" si="7"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A390" t="s">
+        <v>0</v>
+      </c>
+      <c r="B390" t="s">
+        <v>10</v>
+      </c>
+      <c r="C390">
+        <v>190000000</v>
+      </c>
+      <c r="D390" s="4">
+        <v>10</v>
+      </c>
+      <c r="E390">
+        <v>2026</v>
+      </c>
+      <c r="F390" s="3">
+        <f t="shared" si="7"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A391" t="s">
+        <v>0</v>
+      </c>
+      <c r="B391" t="s">
+        <v>10</v>
+      </c>
+      <c r="C391">
+        <v>280000000</v>
+      </c>
+      <c r="D391" s="4">
+        <v>11</v>
+      </c>
+      <c r="E391">
+        <v>2026</v>
+      </c>
+      <c r="F391" s="3">
+        <f t="shared" si="7"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A392" t="s">
+        <v>0</v>
+      </c>
+      <c r="B392" t="s">
+        <v>10</v>
+      </c>
+      <c r="C392">
+        <v>190000000</v>
+      </c>
+      <c r="D392" s="4">
+        <v>12</v>
+      </c>
+      <c r="E392">
+        <v>2026</v>
+      </c>
+      <c r="F392" s="3">
+        <f t="shared" si="7"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A393" t="s">
+        <v>0</v>
+      </c>
+      <c r="B393" t="s">
+        <v>11</v>
+      </c>
+      <c r="C393">
+        <v>270000000</v>
+      </c>
+      <c r="D393" s="4">
+        <v>1</v>
+      </c>
+      <c r="E393">
+        <v>2026</v>
+      </c>
+      <c r="F393" s="3">
+        <f t="shared" si="7"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A394" t="s">
+        <v>0</v>
+      </c>
+      <c r="B394" t="s">
+        <v>11</v>
+      </c>
+      <c r="C394">
+        <v>270000000</v>
+      </c>
+      <c r="D394" s="4">
+        <v>2</v>
+      </c>
+      <c r="E394">
+        <v>2026</v>
+      </c>
+      <c r="F394" s="3">
+        <f t="shared" si="7"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A395" t="s">
+        <v>0</v>
+      </c>
+      <c r="B395" t="s">
+        <v>11</v>
+      </c>
+      <c r="C395">
+        <v>220000000</v>
+      </c>
+      <c r="D395" s="4">
+        <v>3</v>
+      </c>
+      <c r="E395">
+        <v>2026</v>
+      </c>
+      <c r="F395" s="3">
+        <f t="shared" si="7"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A396" t="s">
+        <v>0</v>
+      </c>
+      <c r="B396" t="s">
+        <v>11</v>
+      </c>
+      <c r="C396">
+        <v>225000000</v>
+      </c>
+      <c r="D396" s="4">
+        <v>4</v>
+      </c>
+      <c r="E396">
+        <v>2026</v>
+      </c>
+      <c r="F396" s="3">
+        <f t="shared" si="7"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A397" t="s">
+        <v>0</v>
+      </c>
+      <c r="B397" t="s">
+        <v>11</v>
+      </c>
+      <c r="C397">
+        <v>230000000</v>
+      </c>
+      <c r="D397" s="4">
+        <v>5</v>
+      </c>
+      <c r="E397">
+        <v>2026</v>
+      </c>
+      <c r="F397" s="3">
+        <f t="shared" si="7"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A398" t="s">
+        <v>0</v>
+      </c>
+      <c r="B398" t="s">
+        <v>11</v>
+      </c>
+      <c r="C398">
+        <v>230000000</v>
+      </c>
+      <c r="D398" s="4">
+        <v>6</v>
+      </c>
+      <c r="E398">
+        <v>2026</v>
+      </c>
+      <c r="F398" s="3">
+        <f t="shared" si="7"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="399" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A399" t="s">
+        <v>0</v>
+      </c>
+      <c r="B399" t="s">
+        <v>11</v>
+      </c>
+      <c r="C399">
+        <v>270000000</v>
+      </c>
+      <c r="D399" s="4">
+        <v>7</v>
+      </c>
+      <c r="E399">
+        <v>2026</v>
+      </c>
+      <c r="F399" s="3">
+        <f t="shared" si="7"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A400" t="s">
+        <v>0</v>
+      </c>
+      <c r="B400" t="s">
+        <v>11</v>
+      </c>
+      <c r="C400">
+        <v>430000000</v>
+      </c>
+      <c r="D400" s="4">
+        <v>8</v>
+      </c>
+      <c r="E400">
+        <v>2026</v>
+      </c>
+      <c r="F400" s="3">
+        <f t="shared" si="7"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A401" t="s">
+        <v>0</v>
+      </c>
+      <c r="B401" t="s">
+        <v>11</v>
+      </c>
+      <c r="C401">
+        <v>235000000</v>
+      </c>
+      <c r="D401" s="4">
+        <v>9</v>
+      </c>
+      <c r="E401">
+        <v>2026</v>
+      </c>
+      <c r="F401" s="3">
+        <f t="shared" si="7"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A402" t="s">
+        <v>0</v>
+      </c>
+      <c r="B402" t="s">
+        <v>11</v>
+      </c>
+      <c r="C402">
+        <v>190000000</v>
+      </c>
+      <c r="D402" s="4">
+        <v>10</v>
+      </c>
+      <c r="E402">
+        <v>2026</v>
+      </c>
+      <c r="F402" s="3">
+        <f t="shared" si="7"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A403" t="s">
+        <v>0</v>
+      </c>
+      <c r="B403" t="s">
+        <v>11</v>
+      </c>
+      <c r="C403">
+        <v>300000000</v>
+      </c>
+      <c r="D403" s="4">
+        <v>11</v>
+      </c>
+      <c r="E403">
+        <v>2026</v>
+      </c>
+      <c r="F403" s="3">
+        <f t="shared" si="7"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A404" t="s">
+        <v>0</v>
+      </c>
+      <c r="B404" t="s">
+        <v>11</v>
+      </c>
+      <c r="C404">
+        <v>190000000</v>
+      </c>
+      <c r="D404" s="4">
+        <v>12</v>
+      </c>
+      <c r="E404">
+        <v>2026</v>
+      </c>
+      <c r="F404" s="3">
+        <f t="shared" si="7"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A405" t="s">
+        <v>0</v>
+      </c>
+      <c r="B405" t="s">
+        <v>12</v>
+      </c>
+      <c r="C405">
+        <v>220000000</v>
+      </c>
+      <c r="D405" s="4">
+        <v>1</v>
+      </c>
+      <c r="E405">
+        <v>2026</v>
+      </c>
+      <c r="F405" s="3">
+        <f t="shared" si="7"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A406" t="s">
+        <v>0</v>
+      </c>
+      <c r="B406" t="s">
+        <v>12</v>
+      </c>
+      <c r="C406">
+        <v>220000000</v>
+      </c>
+      <c r="D406" s="4">
+        <v>2</v>
+      </c>
+      <c r="E406">
+        <v>2026</v>
+      </c>
+      <c r="F406" s="3">
+        <f t="shared" si="7"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A407" t="s">
+        <v>0</v>
+      </c>
+      <c r="B407" t="s">
+        <v>12</v>
+      </c>
+      <c r="C407">
+        <v>190000000</v>
+      </c>
+      <c r="D407" s="4">
+        <v>3</v>
+      </c>
+      <c r="E407">
+        <v>2026</v>
+      </c>
+      <c r="F407" s="3">
+        <f t="shared" si="7"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A408" t="s">
+        <v>0</v>
+      </c>
+      <c r="B408" t="s">
+        <v>12</v>
+      </c>
+      <c r="C408">
+        <v>195000000</v>
+      </c>
+      <c r="D408" s="4">
+        <v>4</v>
+      </c>
+      <c r="E408">
+        <v>2026</v>
+      </c>
+      <c r="F408" s="3">
+        <f t="shared" si="7"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A409" t="s">
+        <v>0</v>
+      </c>
+      <c r="B409" t="s">
+        <v>12</v>
+      </c>
+      <c r="C409">
+        <v>200000000</v>
+      </c>
+      <c r="D409" s="4">
+        <v>5</v>
+      </c>
+      <c r="E409">
+        <v>2026</v>
+      </c>
+      <c r="F409" s="3">
+        <f t="shared" si="7"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="410" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A410" t="s">
+        <v>0</v>
+      </c>
+      <c r="B410" t="s">
+        <v>12</v>
+      </c>
+      <c r="C410">
+        <v>220000000</v>
+      </c>
+      <c r="D410" s="4">
+        <v>6</v>
+      </c>
+      <c r="E410">
+        <v>2026</v>
+      </c>
+      <c r="F410" s="3">
+        <f t="shared" si="7"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A411" t="s">
+        <v>0</v>
+      </c>
+      <c r="B411" t="s">
+        <v>12</v>
+      </c>
+      <c r="C411">
+        <v>220000000</v>
+      </c>
+      <c r="D411" s="4">
+        <v>7</v>
+      </c>
+      <c r="E411">
+        <v>2026</v>
+      </c>
+      <c r="F411" s="3">
+        <f t="shared" si="7"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A412" t="s">
+        <v>0</v>
+      </c>
+      <c r="B412" t="s">
+        <v>12</v>
+      </c>
+      <c r="C412">
+        <v>420000000</v>
+      </c>
+      <c r="D412" s="4">
+        <v>8</v>
+      </c>
+      <c r="E412">
+        <v>2026</v>
+      </c>
+      <c r="F412" s="3">
+        <f t="shared" ref="F412:F475" si="8">DATE(E412,D412,1)</f>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="413" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A413" t="s">
+        <v>0</v>
+      </c>
+      <c r="B413" t="s">
+        <v>12</v>
+      </c>
+      <c r="C413">
+        <v>215000000</v>
+      </c>
+      <c r="D413" s="4">
+        <v>9</v>
+      </c>
+      <c r="E413">
+        <v>2026</v>
+      </c>
+      <c r="F413" s="3">
+        <f t="shared" si="8"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="414" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A414" t="s">
+        <v>0</v>
+      </c>
+      <c r="B414" t="s">
+        <v>12</v>
+      </c>
+      <c r="C414">
+        <v>170000000</v>
+      </c>
+      <c r="D414" s="4">
+        <v>10</v>
+      </c>
+      <c r="E414">
+        <v>2026</v>
+      </c>
+      <c r="F414" s="3">
+        <f t="shared" si="8"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="415" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A415" t="s">
+        <v>0</v>
+      </c>
+      <c r="B415" t="s">
+        <v>12</v>
+      </c>
+      <c r="C415">
+        <v>240000000</v>
+      </c>
+      <c r="D415" s="4">
+        <v>11</v>
+      </c>
+      <c r="E415">
+        <v>2026</v>
+      </c>
+      <c r="F415" s="3">
+        <f t="shared" si="8"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="416" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A416" t="s">
+        <v>0</v>
+      </c>
+      <c r="B416" t="s">
+        <v>12</v>
+      </c>
+      <c r="C416">
+        <v>190000000</v>
+      </c>
+      <c r="D416" s="4">
+        <v>12</v>
+      </c>
+      <c r="E416">
+        <v>2026</v>
+      </c>
+      <c r="F416" s="3">
+        <f t="shared" si="8"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="417" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A417" t="s">
+        <v>0</v>
+      </c>
+      <c r="B417" t="s">
+        <v>13</v>
+      </c>
+      <c r="C417">
+        <v>220000000</v>
+      </c>
+      <c r="D417" s="4">
+        <v>1</v>
+      </c>
+      <c r="E417">
+        <v>2026</v>
+      </c>
+      <c r="F417" s="3">
+        <f t="shared" si="8"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="418" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A418" t="s">
+        <v>0</v>
+      </c>
+      <c r="B418" t="s">
+        <v>13</v>
+      </c>
+      <c r="C418">
+        <v>220000000</v>
+      </c>
+      <c r="D418" s="4">
+        <v>2</v>
+      </c>
+      <c r="E418">
+        <v>2026</v>
+      </c>
+      <c r="F418" s="3">
+        <f t="shared" si="8"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="419" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A419" t="s">
+        <v>0</v>
+      </c>
+      <c r="B419" t="s">
+        <v>13</v>
+      </c>
+      <c r="C419">
+        <v>190000000</v>
+      </c>
+      <c r="D419" s="4">
+        <v>3</v>
+      </c>
+      <c r="E419">
+        <v>2026</v>
+      </c>
+      <c r="F419" s="3">
+        <f t="shared" si="8"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="420" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A420" t="s">
+        <v>0</v>
+      </c>
+      <c r="B420" t="s">
+        <v>13</v>
+      </c>
+      <c r="C420">
+        <v>195000000</v>
+      </c>
+      <c r="D420" s="4">
+        <v>4</v>
+      </c>
+      <c r="E420">
+        <v>2026</v>
+      </c>
+      <c r="F420" s="3">
+        <f t="shared" si="8"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="421" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A421" t="s">
+        <v>0</v>
+      </c>
+      <c r="B421" t="s">
+        <v>13</v>
+      </c>
+      <c r="C421">
+        <v>200000000</v>
+      </c>
+      <c r="D421" s="4">
+        <v>5</v>
+      </c>
+      <c r="E421">
+        <v>2026</v>
+      </c>
+      <c r="F421" s="3">
+        <f t="shared" si="8"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="422" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A422" t="s">
+        <v>0</v>
+      </c>
+      <c r="B422" t="s">
+        <v>13</v>
+      </c>
+      <c r="C422">
+        <v>200000000</v>
+      </c>
+      <c r="D422" s="4">
+        <v>6</v>
+      </c>
+      <c r="E422">
+        <v>2026</v>
+      </c>
+      <c r="F422" s="3">
+        <f t="shared" si="8"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="423" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A423" t="s">
+        <v>0</v>
+      </c>
+      <c r="B423" t="s">
+        <v>13</v>
+      </c>
+      <c r="C423">
+        <v>230000000</v>
+      </c>
+      <c r="D423" s="4">
+        <v>7</v>
+      </c>
+      <c r="E423">
+        <v>2026</v>
+      </c>
+      <c r="F423" s="3">
+        <f t="shared" si="8"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="424" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A424" t="s">
+        <v>0</v>
+      </c>
+      <c r="B424" t="s">
+        <v>13</v>
+      </c>
+      <c r="C424">
+        <v>390000000</v>
+      </c>
+      <c r="D424" s="4">
+        <v>8</v>
+      </c>
+      <c r="E424">
+        <v>2026</v>
+      </c>
+      <c r="F424" s="3">
+        <f t="shared" si="8"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A425" t="s">
+        <v>0</v>
+      </c>
+      <c r="B425" t="s">
+        <v>13</v>
+      </c>
+      <c r="C425">
+        <v>195000000</v>
+      </c>
+      <c r="D425" s="4">
+        <v>9</v>
+      </c>
+      <c r="E425">
+        <v>2026</v>
+      </c>
+      <c r="F425" s="3">
+        <f t="shared" si="8"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="426" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A426" t="s">
+        <v>0</v>
+      </c>
+      <c r="B426" t="s">
+        <v>13</v>
+      </c>
+      <c r="C426">
+        <v>170000000</v>
+      </c>
+      <c r="D426" s="4">
+        <v>10</v>
+      </c>
+      <c r="E426">
+        <v>2026</v>
+      </c>
+      <c r="F426" s="3">
+        <f t="shared" si="8"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="427" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A427" t="s">
+        <v>0</v>
+      </c>
+      <c r="B427" t="s">
+        <v>13</v>
+      </c>
+      <c r="C427">
+        <v>230000000</v>
+      </c>
+      <c r="D427" s="4">
+        <v>11</v>
+      </c>
+      <c r="E427">
+        <v>2026</v>
+      </c>
+      <c r="F427" s="3">
+        <f t="shared" si="8"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="428" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A428" t="s">
+        <v>0</v>
+      </c>
+      <c r="B428" t="s">
+        <v>13</v>
+      </c>
+      <c r="C428">
+        <v>180000000</v>
+      </c>
+      <c r="D428" s="4">
+        <v>12</v>
+      </c>
+      <c r="E428">
+        <v>2026</v>
+      </c>
+      <c r="F428" s="3">
+        <f t="shared" si="8"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="429" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A429" t="s">
+        <v>0</v>
+      </c>
+      <c r="B429" t="s">
+        <v>15</v>
+      </c>
+      <c r="C429">
+        <v>230000000</v>
+      </c>
+      <c r="D429" s="4">
+        <v>1</v>
+      </c>
+      <c r="E429">
+        <v>2026</v>
+      </c>
+      <c r="F429" s="3">
+        <f t="shared" si="8"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="430" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A430" t="s">
+        <v>0</v>
+      </c>
+      <c r="B430" t="s">
+        <v>15</v>
+      </c>
+      <c r="C430">
+        <v>230000000</v>
+      </c>
+      <c r="D430" s="4">
+        <v>2</v>
+      </c>
+      <c r="E430">
+        <v>2026</v>
+      </c>
+      <c r="F430" s="3">
+        <f t="shared" si="8"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="431" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A431" t="s">
+        <v>0</v>
+      </c>
+      <c r="B431" t="s">
+        <v>15</v>
+      </c>
+      <c r="C431">
+        <v>190000000</v>
+      </c>
+      <c r="D431" s="4">
+        <v>3</v>
+      </c>
+      <c r="E431">
+        <v>2026</v>
+      </c>
+      <c r="F431" s="3">
+        <f t="shared" si="8"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="432" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A432" t="s">
+        <v>0</v>
+      </c>
+      <c r="B432" t="s">
+        <v>15</v>
+      </c>
+      <c r="C432">
+        <v>195000000</v>
+      </c>
+      <c r="D432" s="4">
+        <v>4</v>
+      </c>
+      <c r="E432">
+        <v>2026</v>
+      </c>
+      <c r="F432" s="3">
+        <f t="shared" si="8"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="433" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A433" t="s">
+        <v>0</v>
+      </c>
+      <c r="B433" t="s">
+        <v>15</v>
+      </c>
+      <c r="C433">
+        <v>210000000</v>
+      </c>
+      <c r="D433" s="4">
+        <v>5</v>
+      </c>
+      <c r="E433">
+        <v>2026</v>
+      </c>
+      <c r="F433" s="3">
+        <f t="shared" si="8"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="434" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A434" t="s">
+        <v>0</v>
+      </c>
+      <c r="B434" t="s">
+        <v>15</v>
+      </c>
+      <c r="C434">
+        <v>210000000</v>
+      </c>
+      <c r="D434" s="4">
+        <v>6</v>
+      </c>
+      <c r="E434">
+        <v>2026</v>
+      </c>
+      <c r="F434" s="3">
+        <f t="shared" si="8"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="435" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A435" t="s">
+        <v>0</v>
+      </c>
+      <c r="B435" t="s">
+        <v>15</v>
+      </c>
+      <c r="C435">
+        <v>240000000</v>
+      </c>
+      <c r="D435" s="4">
+        <v>7</v>
+      </c>
+      <c r="E435">
+        <v>2026</v>
+      </c>
+      <c r="F435" s="3">
+        <f t="shared" si="8"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="436" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A436" t="s">
+        <v>0</v>
+      </c>
+      <c r="B436" t="s">
+        <v>15</v>
+      </c>
+      <c r="C436">
+        <v>430000000</v>
+      </c>
+      <c r="D436" s="4">
+        <v>8</v>
+      </c>
+      <c r="E436">
+        <v>2026</v>
+      </c>
+      <c r="F436" s="3">
+        <f t="shared" si="8"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="437" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A437" t="s">
+        <v>0</v>
+      </c>
+      <c r="B437" t="s">
+        <v>15</v>
+      </c>
+      <c r="C437">
+        <v>215000000</v>
+      </c>
+      <c r="D437" s="4">
+        <v>9</v>
+      </c>
+      <c r="E437">
+        <v>2026</v>
+      </c>
+      <c r="F437" s="3">
+        <f t="shared" si="8"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="438" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A438" t="s">
+        <v>0</v>
+      </c>
+      <c r="B438" t="s">
+        <v>15</v>
+      </c>
+      <c r="C438">
+        <v>180000000</v>
+      </c>
+      <c r="D438" s="4">
+        <v>10</v>
+      </c>
+      <c r="E438">
+        <v>2026</v>
+      </c>
+      <c r="F438" s="3">
+        <f t="shared" si="8"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="439" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A439" t="s">
+        <v>0</v>
+      </c>
+      <c r="B439" t="s">
+        <v>15</v>
+      </c>
+      <c r="C439">
+        <v>270000000</v>
+      </c>
+      <c r="D439" s="4">
+        <v>11</v>
+      </c>
+      <c r="E439">
+        <v>2026</v>
+      </c>
+      <c r="F439" s="3">
+        <f t="shared" si="8"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="440" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A440" t="s">
+        <v>0</v>
+      </c>
+      <c r="B440" t="s">
+        <v>15</v>
+      </c>
+      <c r="C440">
+        <v>190000000</v>
+      </c>
+      <c r="D440" s="4">
+        <v>12</v>
+      </c>
+      <c r="E440">
+        <v>2026</v>
+      </c>
+      <c r="F440" s="3">
+        <f t="shared" si="8"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="441" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A441" t="s">
+        <v>0</v>
+      </c>
+      <c r="B441" t="s">
+        <v>7</v>
+      </c>
+      <c r="C441">
+        <v>220000000</v>
+      </c>
+      <c r="D441" s="4">
+        <v>1</v>
+      </c>
+      <c r="E441">
+        <v>2026</v>
+      </c>
+      <c r="F441" s="3">
+        <f t="shared" si="8"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="442" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A442" t="s">
+        <v>0</v>
+      </c>
+      <c r="B442" t="s">
+        <v>7</v>
+      </c>
+      <c r="C442">
+        <v>210000000</v>
+      </c>
+      <c r="D442" s="4">
+        <v>2</v>
+      </c>
+      <c r="E442">
+        <v>2026</v>
+      </c>
+      <c r="F442" s="3">
+        <f t="shared" si="8"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="443" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A443" t="s">
+        <v>0</v>
+      </c>
+      <c r="B443" t="s">
+        <v>7</v>
+      </c>
+      <c r="C443">
+        <v>200000000</v>
+      </c>
+      <c r="D443" s="4">
+        <v>3</v>
+      </c>
+      <c r="E443">
+        <v>2026</v>
+      </c>
+      <c r="F443" s="3">
+        <f t="shared" si="8"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="444" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A444" t="s">
+        <v>0</v>
+      </c>
+      <c r="B444" t="s">
+        <v>7</v>
+      </c>
+      <c r="C444">
+        <v>195000000</v>
+      </c>
+      <c r="D444" s="4">
+        <v>4</v>
+      </c>
+      <c r="E444">
+        <v>2026</v>
+      </c>
+      <c r="F444" s="3">
+        <f t="shared" si="8"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="445" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A445" t="s">
+        <v>0</v>
+      </c>
+      <c r="B445" t="s">
+        <v>7</v>
+      </c>
+      <c r="C445">
+        <v>200000000</v>
+      </c>
+      <c r="D445" s="4">
+        <v>5</v>
+      </c>
+      <c r="E445">
+        <v>2026</v>
+      </c>
+      <c r="F445" s="3">
+        <f t="shared" si="8"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="446" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A446" t="s">
+        <v>0</v>
+      </c>
+      <c r="B446" t="s">
+        <v>7</v>
+      </c>
+      <c r="C446">
+        <v>220000000</v>
+      </c>
+      <c r="D446" s="4">
+        <v>6</v>
+      </c>
+      <c r="E446">
+        <v>2026</v>
+      </c>
+      <c r="F446" s="3">
+        <f t="shared" si="8"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="447" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A447" t="s">
+        <v>0</v>
+      </c>
+      <c r="B447" t="s">
+        <v>7</v>
+      </c>
+      <c r="C447">
+        <v>210000000</v>
+      </c>
+      <c r="D447" s="4">
+        <v>7</v>
+      </c>
+      <c r="E447">
+        <v>2026</v>
+      </c>
+      <c r="F447" s="3">
+        <f t="shared" si="8"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="448" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A448" t="s">
+        <v>0</v>
+      </c>
+      <c r="B448" t="s">
+        <v>7</v>
+      </c>
+      <c r="C448">
+        <v>300000000</v>
+      </c>
+      <c r="D448" s="4">
+        <v>8</v>
+      </c>
+      <c r="E448">
+        <v>2026</v>
+      </c>
+      <c r="F448" s="3">
+        <f t="shared" si="8"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="449" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A449" t="s">
+        <v>0</v>
+      </c>
+      <c r="B449" t="s">
+        <v>7</v>
+      </c>
+      <c r="C449">
+        <v>195000000</v>
+      </c>
+      <c r="D449" s="4">
+        <v>9</v>
+      </c>
+      <c r="E449">
+        <v>2026</v>
+      </c>
+      <c r="F449" s="3">
+        <f t="shared" si="8"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A450" t="s">
+        <v>0</v>
+      </c>
+      <c r="B450" t="s">
+        <v>7</v>
+      </c>
+      <c r="C450">
+        <v>160000000</v>
+      </c>
+      <c r="D450" s="4">
+        <v>10</v>
+      </c>
+      <c r="E450">
+        <v>2026</v>
+      </c>
+      <c r="F450" s="3">
+        <f t="shared" si="8"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="451" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A451" t="s">
+        <v>0</v>
+      </c>
+      <c r="B451" t="s">
+        <v>7</v>
+      </c>
+      <c r="C451">
+        <v>240000000</v>
+      </c>
+      <c r="D451" s="4">
+        <v>11</v>
+      </c>
+      <c r="E451">
+        <v>2026</v>
+      </c>
+      <c r="F451" s="3">
+        <f t="shared" si="8"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="452" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A452" t="s">
+        <v>0</v>
+      </c>
+      <c r="B452" t="s">
+        <v>7</v>
+      </c>
+      <c r="C452">
+        <v>170000000</v>
+      </c>
+      <c r="D452" s="4">
+        <v>12</v>
+      </c>
+      <c r="E452">
+        <v>2026</v>
+      </c>
+      <c r="F452" s="3">
+        <f t="shared" si="8"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="453" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A453" t="s">
+        <v>0</v>
+      </c>
+      <c r="B453" t="s">
+        <v>14</v>
+      </c>
+      <c r="C453">
+        <v>250000000</v>
+      </c>
+      <c r="D453" s="4">
+        <v>1</v>
+      </c>
+      <c r="E453">
+        <v>2026</v>
+      </c>
+      <c r="F453" s="3">
+        <f t="shared" si="8"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="454" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A454" t="s">
+        <v>0</v>
+      </c>
+      <c r="B454" t="s">
+        <v>14</v>
+      </c>
+      <c r="C454">
+        <v>250000000</v>
+      </c>
+      <c r="D454" s="4">
+        <v>2</v>
+      </c>
+      <c r="E454">
+        <v>2026</v>
+      </c>
+      <c r="F454" s="3">
+        <f t="shared" si="8"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="455" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A455" t="s">
+        <v>0</v>
+      </c>
+      <c r="B455" t="s">
+        <v>14</v>
+      </c>
+      <c r="C455">
+        <v>210000000</v>
+      </c>
+      <c r="D455" s="4">
+        <v>3</v>
+      </c>
+      <c r="E455">
+        <v>2026</v>
+      </c>
+      <c r="F455" s="3">
+        <f t="shared" si="8"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="456" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A456" t="s">
+        <v>0</v>
+      </c>
+      <c r="B456" t="s">
+        <v>14</v>
+      </c>
+      <c r="C456">
+        <v>215000000</v>
+      </c>
+      <c r="D456" s="4">
+        <v>4</v>
+      </c>
+      <c r="E456">
+        <v>2026</v>
+      </c>
+      <c r="F456" s="3">
+        <f t="shared" si="8"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="457" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A457" t="s">
+        <v>0</v>
+      </c>
+      <c r="B457" t="s">
+        <v>14</v>
+      </c>
+      <c r="C457">
+        <v>220000000</v>
+      </c>
+      <c r="D457" s="4">
+        <v>5</v>
+      </c>
+      <c r="E457">
+        <v>2026</v>
+      </c>
+      <c r="F457" s="3">
+        <f t="shared" si="8"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="458" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A458" t="s">
+        <v>0</v>
+      </c>
+      <c r="B458" t="s">
+        <v>14</v>
+      </c>
+      <c r="C458">
+        <v>220000000</v>
+      </c>
+      <c r="D458" s="4">
+        <v>6</v>
+      </c>
+      <c r="E458">
+        <v>2026</v>
+      </c>
+      <c r="F458" s="3">
+        <f t="shared" si="8"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="459" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A459" t="s">
+        <v>0</v>
+      </c>
+      <c r="B459" t="s">
+        <v>14</v>
+      </c>
+      <c r="C459">
+        <v>240000000</v>
+      </c>
+      <c r="D459" s="4">
+        <v>7</v>
+      </c>
+      <c r="E459">
+        <v>2026</v>
+      </c>
+      <c r="F459" s="3">
+        <f t="shared" si="8"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="460" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A460" t="s">
+        <v>0</v>
+      </c>
+      <c r="B460" t="s">
+        <v>14</v>
+      </c>
+      <c r="C460">
+        <v>450000000</v>
+      </c>
+      <c r="D460" s="4">
+        <v>8</v>
+      </c>
+      <c r="E460">
+        <v>2026</v>
+      </c>
+      <c r="F460" s="3">
+        <f t="shared" si="8"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="461" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A461" t="s">
+        <v>0</v>
+      </c>
+      <c r="B461" t="s">
+        <v>14</v>
+      </c>
+      <c r="C461">
+        <v>215000000</v>
+      </c>
+      <c r="D461" s="4">
+        <v>9</v>
+      </c>
+      <c r="E461">
+        <v>2026</v>
+      </c>
+      <c r="F461" s="3">
+        <f t="shared" si="8"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="462" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A462" t="s">
+        <v>0</v>
+      </c>
+      <c r="B462" t="s">
+        <v>14</v>
+      </c>
+      <c r="C462">
+        <v>180000000</v>
+      </c>
+      <c r="D462" s="4">
+        <v>10</v>
+      </c>
+      <c r="E462">
+        <v>2026</v>
+      </c>
+      <c r="F462" s="3">
+        <f t="shared" si="8"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="463" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A463" t="s">
+        <v>0</v>
+      </c>
+      <c r="B463" t="s">
+        <v>14</v>
+      </c>
+      <c r="C463">
+        <v>260000000</v>
+      </c>
+      <c r="D463" s="4">
+        <v>11</v>
+      </c>
+      <c r="E463">
+        <v>2026</v>
+      </c>
+      <c r="F463" s="3">
+        <f t="shared" si="8"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="464" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A464" t="s">
+        <v>0</v>
+      </c>
+      <c r="B464" t="s">
+        <v>14</v>
+      </c>
+      <c r="C464">
+        <v>190000000</v>
+      </c>
+      <c r="D464" s="4">
+        <v>12</v>
+      </c>
+      <c r="E464">
+        <v>2026</v>
+      </c>
+      <c r="F464" s="3">
+        <f t="shared" si="8"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="465" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A465" t="s">
+        <v>0</v>
+      </c>
+      <c r="B465" t="s">
+        <v>5</v>
+      </c>
+      <c r="C465">
+        <v>250000000</v>
+      </c>
+      <c r="D465" s="4">
+        <v>1</v>
+      </c>
+      <c r="E465">
+        <v>2026</v>
+      </c>
+      <c r="F465" s="3">
+        <f t="shared" si="8"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="466" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A466" t="s">
+        <v>0</v>
+      </c>
+      <c r="B466" t="s">
+        <v>5</v>
+      </c>
+      <c r="C466">
+        <v>250000000</v>
+      </c>
+      <c r="D466" s="4">
+        <v>2</v>
+      </c>
+      <c r="E466">
+        <v>2026</v>
+      </c>
+      <c r="F466" s="3">
+        <f t="shared" si="8"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="467" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A467" t="s">
+        <v>0</v>
+      </c>
+      <c r="B467" t="s">
+        <v>5</v>
+      </c>
+      <c r="C467">
+        <v>220000000</v>
+      </c>
+      <c r="D467" s="4">
+        <v>3</v>
+      </c>
+      <c r="E467">
+        <v>2026</v>
+      </c>
+      <c r="F467" s="3">
+        <f t="shared" si="8"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="468" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A468" t="s">
+        <v>0</v>
+      </c>
+      <c r="B468" t="s">
+        <v>5</v>
+      </c>
+      <c r="C468">
+        <v>225000000</v>
+      </c>
+      <c r="D468" s="4">
+        <v>4</v>
+      </c>
+      <c r="E468">
+        <v>2026</v>
+      </c>
+      <c r="F468" s="3">
+        <f t="shared" si="8"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="469" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A469" t="s">
+        <v>0</v>
+      </c>
+      <c r="B469" t="s">
+        <v>5</v>
+      </c>
+      <c r="C469">
+        <v>230000000</v>
+      </c>
+      <c r="D469" s="4">
+        <v>5</v>
+      </c>
+      <c r="E469">
+        <v>2026</v>
+      </c>
+      <c r="F469" s="3">
+        <f t="shared" si="8"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="470" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A470" t="s">
+        <v>0</v>
+      </c>
+      <c r="B470" t="s">
+        <v>5</v>
+      </c>
+      <c r="C470">
+        <v>230000000</v>
+      </c>
+      <c r="D470" s="4">
+        <v>6</v>
+      </c>
+      <c r="E470">
+        <v>2026</v>
+      </c>
+      <c r="F470" s="3">
+        <f t="shared" si="8"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="471" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A471" t="s">
+        <v>0</v>
+      </c>
+      <c r="B471" t="s">
+        <v>5</v>
+      </c>
+      <c r="C471">
+        <v>280000000</v>
+      </c>
+      <c r="D471" s="4">
+        <v>7</v>
+      </c>
+      <c r="E471">
+        <v>2026</v>
+      </c>
+      <c r="F471" s="3">
+        <f t="shared" si="8"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="472" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A472" t="s">
+        <v>0</v>
+      </c>
+      <c r="B472" t="s">
+        <v>5</v>
+      </c>
+      <c r="C472">
+        <v>440000000</v>
+      </c>
+      <c r="D472" s="4">
+        <v>8</v>
+      </c>
+      <c r="E472">
+        <v>2026</v>
+      </c>
+      <c r="F472" s="3">
+        <f t="shared" si="8"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="473" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A473" t="s">
+        <v>0</v>
+      </c>
+      <c r="B473" t="s">
+        <v>5</v>
+      </c>
+      <c r="C473">
+        <v>240000000</v>
+      </c>
+      <c r="D473" s="4">
+        <v>9</v>
+      </c>
+      <c r="E473">
+        <v>2026</v>
+      </c>
+      <c r="F473" s="3">
+        <f t="shared" si="8"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="474" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A474" t="s">
+        <v>0</v>
+      </c>
+      <c r="B474" t="s">
+        <v>5</v>
+      </c>
+      <c r="C474">
+        <v>190000000</v>
+      </c>
+      <c r="D474" s="4">
+        <v>10</v>
+      </c>
+      <c r="E474">
+        <v>2026</v>
+      </c>
+      <c r="F474" s="3">
+        <f t="shared" si="8"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="475" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A475" t="s">
+        <v>0</v>
+      </c>
+      <c r="B475" t="s">
+        <v>5</v>
+      </c>
+      <c r="C475">
+        <v>320000000</v>
+      </c>
+      <c r="D475" s="4">
+        <v>11</v>
+      </c>
+      <c r="E475">
+        <v>2026</v>
+      </c>
+      <c r="F475" s="3">
+        <f t="shared" si="8"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="476" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A476" t="s">
+        <v>0</v>
+      </c>
+      <c r="B476" t="s">
+        <v>5</v>
+      </c>
+      <c r="C476">
+        <v>190000000</v>
+      </c>
+      <c r="D476" s="4">
+        <v>12</v>
+      </c>
+      <c r="E476">
+        <v>2026</v>
+      </c>
+      <c r="F476" s="3">
+        <f t="shared" ref="F476:F539" si="9">DATE(E476,D476,1)</f>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="477" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A477" t="s">
+        <v>0</v>
+      </c>
+      <c r="B477" t="s">
+        <v>6</v>
+      </c>
+      <c r="C477">
+        <v>380000000</v>
+      </c>
+      <c r="D477" s="4">
+        <v>1</v>
+      </c>
+      <c r="E477">
+        <v>2026</v>
+      </c>
+      <c r="F477" s="3">
+        <f t="shared" si="9"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="478" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A478" t="s">
+        <v>0</v>
+      </c>
+      <c r="B478" t="s">
+        <v>6</v>
+      </c>
+      <c r="C478">
+        <v>360000000</v>
+      </c>
+      <c r="D478" s="4">
+        <v>2</v>
+      </c>
+      <c r="E478">
+        <v>2026</v>
+      </c>
+      <c r="F478" s="3">
+        <f t="shared" si="9"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="479" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A479" t="s">
+        <v>0</v>
+      </c>
+      <c r="B479" t="s">
+        <v>6</v>
+      </c>
+      <c r="C479">
+        <v>280000000</v>
+      </c>
+      <c r="D479" s="4">
+        <v>3</v>
+      </c>
+      <c r="E479">
+        <v>2026</v>
+      </c>
+      <c r="F479" s="3">
+        <f t="shared" si="9"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="480" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A480" t="s">
+        <v>0</v>
+      </c>
+      <c r="B480" t="s">
+        <v>6</v>
+      </c>
+      <c r="C480">
+        <v>285000000</v>
+      </c>
+      <c r="D480" s="4">
+        <v>4</v>
+      </c>
+      <c r="E480">
+        <v>2026</v>
+      </c>
+      <c r="F480" s="3">
+        <f t="shared" si="9"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="481" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A481" t="s">
+        <v>0</v>
+      </c>
+      <c r="B481" t="s">
+        <v>6</v>
+      </c>
+      <c r="C481">
+        <v>280000000</v>
+      </c>
+      <c r="D481" s="4">
+        <v>5</v>
+      </c>
+      <c r="E481">
+        <v>2026</v>
+      </c>
+      <c r="F481" s="3">
+        <f t="shared" si="9"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="482" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A482" t="s">
+        <v>0</v>
+      </c>
+      <c r="B482" t="s">
+        <v>6</v>
+      </c>
+      <c r="C482">
+        <v>280000000</v>
+      </c>
+      <c r="D482" s="4">
+        <v>6</v>
+      </c>
+      <c r="E482">
+        <v>2026</v>
+      </c>
+      <c r="F482" s="3">
+        <f t="shared" si="9"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="483" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A483" t="s">
+        <v>0</v>
+      </c>
+      <c r="B483" t="s">
+        <v>6</v>
+      </c>
+      <c r="C483">
+        <v>345000000</v>
+      </c>
+      <c r="D483" s="4">
+        <v>7</v>
+      </c>
+      <c r="E483">
+        <v>2026</v>
+      </c>
+      <c r="F483" s="3">
+        <f t="shared" si="9"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="484" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A484" t="s">
+        <v>0</v>
+      </c>
+      <c r="B484" t="s">
+        <v>6</v>
+      </c>
+      <c r="C484">
+        <v>620000000</v>
+      </c>
+      <c r="D484" s="4">
+        <v>8</v>
+      </c>
+      <c r="E484">
+        <v>2026</v>
+      </c>
+      <c r="F484" s="3">
+        <f t="shared" si="9"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="485" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A485" t="s">
+        <v>0</v>
+      </c>
+      <c r="B485" t="s">
+        <v>6</v>
+      </c>
+      <c r="C485">
+        <v>320000000</v>
+      </c>
+      <c r="D485" s="4">
+        <v>9</v>
+      </c>
+      <c r="E485">
+        <v>2026</v>
+      </c>
+      <c r="F485" s="3">
+        <f t="shared" si="9"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="486" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A486" t="s">
+        <v>0</v>
+      </c>
+      <c r="B486" t="s">
+        <v>6</v>
+      </c>
+      <c r="C486">
+        <v>230000000</v>
+      </c>
+      <c r="D486" s="4">
+        <v>10</v>
+      </c>
+      <c r="E486">
+        <v>2026</v>
+      </c>
+      <c r="F486" s="3">
+        <f t="shared" si="9"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="487" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A487" t="s">
+        <v>0</v>
+      </c>
+      <c r="B487" t="s">
+        <v>6</v>
+      </c>
+      <c r="C487">
+        <v>390000000</v>
+      </c>
+      <c r="D487" s="4">
+        <v>11</v>
+      </c>
+      <c r="E487">
+        <v>2026</v>
+      </c>
+      <c r="F487" s="3">
+        <f t="shared" si="9"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="488" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A488" t="s">
+        <v>0</v>
+      </c>
+      <c r="B488" t="s">
+        <v>6</v>
+      </c>
+      <c r="C488">
+        <v>250000000</v>
+      </c>
+      <c r="D488" s="4">
+        <v>12</v>
+      </c>
+      <c r="E488">
+        <v>2026</v>
+      </c>
+      <c r="F488" s="3">
+        <f t="shared" si="9"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="489" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A489" t="s">
+        <v>0</v>
+      </c>
+      <c r="B489" t="s">
+        <v>8</v>
+      </c>
+      <c r="C489">
+        <v>200000000</v>
+      </c>
+      <c r="D489" s="4">
+        <v>1</v>
+      </c>
+      <c r="E489">
+        <v>2026</v>
+      </c>
+      <c r="F489" s="3">
+        <f t="shared" si="9"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="490" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A490" t="s">
+        <v>0</v>
+      </c>
+      <c r="B490" t="s">
+        <v>8</v>
+      </c>
+      <c r="C490">
+        <v>200000000</v>
+      </c>
+      <c r="D490" s="4">
+        <v>2</v>
+      </c>
+      <c r="E490">
+        <v>2026</v>
+      </c>
+      <c r="F490" s="3">
+        <f t="shared" si="9"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="491" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A491" t="s">
+        <v>0</v>
+      </c>
+      <c r="B491" t="s">
+        <v>8</v>
+      </c>
+      <c r="C491">
+        <v>190000000</v>
+      </c>
+      <c r="D491" s="4">
+        <v>3</v>
+      </c>
+      <c r="E491">
+        <v>2026</v>
+      </c>
+      <c r="F491" s="3">
+        <f t="shared" si="9"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="492" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A492" t="s">
+        <v>0</v>
+      </c>
+      <c r="B492" t="s">
+        <v>8</v>
+      </c>
+      <c r="C492">
+        <v>185000000</v>
+      </c>
+      <c r="D492" s="4">
+        <v>4</v>
+      </c>
+      <c r="E492">
+        <v>2026</v>
+      </c>
+      <c r="F492" s="3">
+        <f t="shared" si="9"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="493" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A493" t="s">
+        <v>0</v>
+      </c>
+      <c r="B493" t="s">
+        <v>8</v>
+      </c>
+      <c r="C493">
+        <v>200000000</v>
+      </c>
+      <c r="D493" s="4">
+        <v>5</v>
+      </c>
+      <c r="E493">
+        <v>2026</v>
+      </c>
+      <c r="F493" s="3">
+        <f t="shared" si="9"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="494" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A494" t="s">
+        <v>0</v>
+      </c>
+      <c r="B494" t="s">
+        <v>8</v>
+      </c>
+      <c r="C494">
+        <v>200000000</v>
+      </c>
+      <c r="D494" s="4">
+        <v>6</v>
+      </c>
+      <c r="E494">
+        <v>2026</v>
+      </c>
+      <c r="F494" s="3">
+        <f t="shared" si="9"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="495" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A495" t="s">
+        <v>0</v>
+      </c>
+      <c r="B495" t="s">
+        <v>8</v>
+      </c>
+      <c r="C495">
+        <v>200000000</v>
+      </c>
+      <c r="D495" s="4">
+        <v>7</v>
+      </c>
+      <c r="E495">
+        <v>2026</v>
+      </c>
+      <c r="F495" s="3">
+        <f t="shared" si="9"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="496" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A496" t="s">
+        <v>0</v>
+      </c>
+      <c r="B496" t="s">
+        <v>8</v>
+      </c>
+      <c r="C496">
+        <v>330000000</v>
+      </c>
+      <c r="D496" s="4">
+        <v>8</v>
+      </c>
+      <c r="E496">
+        <v>2026</v>
+      </c>
+      <c r="F496" s="3">
+        <f t="shared" si="9"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="497" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A497" t="s">
+        <v>0</v>
+      </c>
+      <c r="B497" t="s">
+        <v>8</v>
+      </c>
+      <c r="C497">
+        <v>195000000</v>
+      </c>
+      <c r="D497" s="4">
+        <v>9</v>
+      </c>
+      <c r="E497">
+        <v>2026</v>
+      </c>
+      <c r="F497" s="3">
+        <f t="shared" si="9"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="498" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A498" t="s">
+        <v>0</v>
+      </c>
+      <c r="B498" t="s">
+        <v>8</v>
+      </c>
+      <c r="C498">
+        <v>160000000</v>
+      </c>
+      <c r="D498" s="4">
+        <v>10</v>
+      </c>
+      <c r="E498">
+        <v>2026</v>
+      </c>
+      <c r="F498" s="3">
+        <f t="shared" si="9"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="499" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A499" t="s">
+        <v>0</v>
+      </c>
+      <c r="B499" t="s">
+        <v>8</v>
+      </c>
+      <c r="C499">
+        <v>240000000</v>
+      </c>
+      <c r="D499" s="4">
+        <v>11</v>
+      </c>
+      <c r="E499">
+        <v>2026</v>
+      </c>
+      <c r="F499" s="3">
+        <f t="shared" si="9"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="500" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A500" t="s">
+        <v>0</v>
+      </c>
+      <c r="B500" t="s">
+        <v>8</v>
+      </c>
+      <c r="C500">
+        <v>170000000</v>
+      </c>
+      <c r="D500" s="4">
+        <v>12</v>
+      </c>
+      <c r="E500">
+        <v>2026</v>
+      </c>
+      <c r="F500" s="3">
+        <f t="shared" si="9"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A501" t="s">
+        <v>0</v>
+      </c>
+      <c r="B501" t="s">
+        <v>16</v>
+      </c>
+      <c r="C501">
+        <v>350000000</v>
+      </c>
+      <c r="D501" s="4">
+        <v>1</v>
+      </c>
+      <c r="E501">
+        <v>2026</v>
+      </c>
+      <c r="F501" s="3">
+        <f t="shared" si="9"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="502" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A502" t="s">
+        <v>0</v>
+      </c>
+      <c r="B502" t="s">
+        <v>16</v>
+      </c>
+      <c r="C502">
+        <v>310000000</v>
+      </c>
+      <c r="D502" s="4">
+        <v>2</v>
+      </c>
+      <c r="E502">
+        <v>2026</v>
+      </c>
+      <c r="F502" s="3">
+        <f t="shared" si="9"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="503" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A503" t="s">
+        <v>0</v>
+      </c>
+      <c r="B503" t="s">
+        <v>16</v>
+      </c>
+      <c r="C503">
+        <v>260000000</v>
+      </c>
+      <c r="D503" s="4">
+        <v>3</v>
+      </c>
+      <c r="E503">
+        <v>2026</v>
+      </c>
+      <c r="F503" s="3">
+        <f t="shared" si="9"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="504" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A504" t="s">
+        <v>0</v>
+      </c>
+      <c r="B504" t="s">
+        <v>16</v>
+      </c>
+      <c r="C504">
+        <v>255000000</v>
+      </c>
+      <c r="D504" s="4">
+        <v>4</v>
+      </c>
+      <c r="E504">
+        <v>2026</v>
+      </c>
+      <c r="F504" s="3">
+        <f t="shared" si="9"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="505" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A505" t="s">
+        <v>0</v>
+      </c>
+      <c r="B505" t="s">
+        <v>16</v>
+      </c>
+      <c r="C505">
+        <v>260000000</v>
+      </c>
+      <c r="D505" s="4">
+        <v>5</v>
+      </c>
+      <c r="E505">
+        <v>2026</v>
+      </c>
+      <c r="F505" s="3">
+        <f t="shared" si="9"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="506" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A506" t="s">
+        <v>0</v>
+      </c>
+      <c r="B506" t="s">
+        <v>16</v>
+      </c>
+      <c r="C506">
+        <v>260000000</v>
+      </c>
+      <c r="D506" s="4">
+        <v>6</v>
+      </c>
+      <c r="E506">
+        <v>2026</v>
+      </c>
+      <c r="F506" s="3">
+        <f t="shared" si="9"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="507" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A507" t="s">
+        <v>0</v>
+      </c>
+      <c r="B507" t="s">
+        <v>16</v>
+      </c>
+      <c r="C507">
+        <v>335000000</v>
+      </c>
+      <c r="D507" s="4">
+        <v>7</v>
+      </c>
+      <c r="E507">
+        <v>2026</v>
+      </c>
+      <c r="F507" s="3">
+        <f t="shared" si="9"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="508" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A508" t="s">
+        <v>0</v>
+      </c>
+      <c r="B508" t="s">
+        <v>16</v>
+      </c>
+      <c r="C508">
+        <v>620000000</v>
+      </c>
+      <c r="D508" s="4">
+        <v>8</v>
+      </c>
+      <c r="E508">
+        <v>2026</v>
+      </c>
+      <c r="F508" s="3">
+        <f t="shared" si="9"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="509" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A509" t="s">
+        <v>0</v>
+      </c>
+      <c r="B509" t="s">
+        <v>16</v>
+      </c>
+      <c r="C509">
+        <v>295000000</v>
+      </c>
+      <c r="D509" s="4">
+        <v>9</v>
+      </c>
+      <c r="E509">
+        <v>2026</v>
+      </c>
+      <c r="F509" s="3">
+        <f t="shared" si="9"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="510" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A510" t="s">
+        <v>0</v>
+      </c>
+      <c r="B510" t="s">
+        <v>16</v>
+      </c>
+      <c r="C510">
+        <v>210000000</v>
+      </c>
+      <c r="D510" s="4">
+        <v>10</v>
+      </c>
+      <c r="E510">
+        <v>2026</v>
+      </c>
+      <c r="F510" s="3">
+        <f t="shared" si="9"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="511" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A511" t="s">
+        <v>0</v>
+      </c>
+      <c r="B511" t="s">
+        <v>16</v>
+      </c>
+      <c r="C511">
+        <v>340000000</v>
+      </c>
+      <c r="D511" s="4">
+        <v>11</v>
+      </c>
+      <c r="E511">
+        <v>2026</v>
+      </c>
+      <c r="F511" s="3">
+        <f t="shared" si="9"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="512" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A512" t="s">
+        <v>0</v>
+      </c>
+      <c r="B512" t="s">
+        <v>16</v>
+      </c>
+      <c r="C512">
+        <v>210000000</v>
+      </c>
+      <c r="D512" s="4">
+        <v>12</v>
+      </c>
+      <c r="E512">
+        <v>2026</v>
+      </c>
+      <c r="F512" s="3">
+        <f t="shared" si="9"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="513" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A513" t="s">
+        <v>0</v>
+      </c>
+      <c r="B513" t="s">
+        <v>24</v>
+      </c>
+      <c r="C513">
+        <v>200000000</v>
+      </c>
+      <c r="D513" s="4">
+        <v>1</v>
+      </c>
+      <c r="E513">
+        <v>2026</v>
+      </c>
+      <c r="F513" s="3">
+        <f t="shared" si="9"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="514" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A514" t="s">
+        <v>0</v>
+      </c>
+      <c r="B514" t="s">
+        <v>24</v>
+      </c>
+      <c r="C514">
+        <v>200000000</v>
+      </c>
+      <c r="D514" s="4">
+        <v>2</v>
+      </c>
+      <c r="E514">
+        <v>2026</v>
+      </c>
+      <c r="F514" s="3">
+        <f t="shared" si="9"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="515" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A515" t="s">
+        <v>0</v>
+      </c>
+      <c r="B515" t="s">
+        <v>24</v>
+      </c>
+      <c r="C515">
+        <v>190000000</v>
+      </c>
+      <c r="D515" s="4">
+        <v>3</v>
+      </c>
+      <c r="E515">
+        <v>2026</v>
+      </c>
+      <c r="F515" s="3">
+        <f t="shared" si="9"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="516" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A516" t="s">
+        <v>0</v>
+      </c>
+      <c r="B516" t="s">
+        <v>24</v>
+      </c>
+      <c r="C516">
+        <v>185000000</v>
+      </c>
+      <c r="D516" s="4">
+        <v>4</v>
+      </c>
+      <c r="E516">
+        <v>2026</v>
+      </c>
+      <c r="F516" s="3">
+        <f t="shared" si="9"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="517" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A517" t="s">
+        <v>0</v>
+      </c>
+      <c r="B517" t="s">
+        <v>24</v>
+      </c>
+      <c r="C517">
+        <v>190000000</v>
+      </c>
+      <c r="D517" s="4">
+        <v>5</v>
+      </c>
+      <c r="E517">
+        <v>2026</v>
+      </c>
+      <c r="F517" s="3">
+        <f t="shared" si="9"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="518" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A518" t="s">
+        <v>0</v>
+      </c>
+      <c r="B518" t="s">
+        <v>24</v>
+      </c>
+      <c r="C518">
+        <v>200000000</v>
+      </c>
+      <c r="D518" s="4">
+        <v>6</v>
+      </c>
+      <c r="E518">
+        <v>2026</v>
+      </c>
+      <c r="F518" s="3">
+        <f t="shared" si="9"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="519" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A519" t="s">
+        <v>0</v>
+      </c>
+      <c r="B519" t="s">
+        <v>24</v>
+      </c>
+      <c r="C519">
+        <v>190000000</v>
+      </c>
+      <c r="D519" s="4">
+        <v>7</v>
+      </c>
+      <c r="E519">
+        <v>2026</v>
+      </c>
+      <c r="F519" s="3">
+        <f t="shared" si="9"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="520" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A520" t="s">
+        <v>0</v>
+      </c>
+      <c r="B520" t="s">
+        <v>24</v>
+      </c>
+      <c r="C520">
+        <v>330000000</v>
+      </c>
+      <c r="D520" s="4">
+        <v>8</v>
+      </c>
+      <c r="E520">
+        <v>2026</v>
+      </c>
+      <c r="F520" s="3">
+        <f t="shared" si="9"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="521" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A521" t="s">
+        <v>0</v>
+      </c>
+      <c r="B521" t="s">
+        <v>24</v>
+      </c>
+      <c r="C521">
+        <v>195000000</v>
+      </c>
+      <c r="D521" s="4">
+        <v>9</v>
+      </c>
+      <c r="E521">
+        <v>2026</v>
+      </c>
+      <c r="F521" s="3">
+        <f t="shared" si="9"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="522" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A522" t="s">
+        <v>0</v>
+      </c>
+      <c r="B522" t="s">
+        <v>24</v>
+      </c>
+      <c r="C522">
+        <v>160000000</v>
+      </c>
+      <c r="D522" s="4">
+        <v>10</v>
+      </c>
+      <c r="E522">
+        <v>2026</v>
+      </c>
+      <c r="F522" s="3">
+        <f t="shared" si="9"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="523" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A523" t="s">
+        <v>0</v>
+      </c>
+      <c r="B523" t="s">
+        <v>24</v>
+      </c>
+      <c r="C523">
+        <v>220000000</v>
+      </c>
+      <c r="D523" s="4">
+        <v>11</v>
+      </c>
+      <c r="E523">
+        <v>2026</v>
+      </c>
+      <c r="F523" s="3">
+        <f t="shared" si="9"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="524" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A524" t="s">
+        <v>0</v>
+      </c>
+      <c r="B524" t="s">
+        <v>24</v>
+      </c>
+      <c r="C524">
+        <v>170000000</v>
+      </c>
+      <c r="D524" s="4">
+        <v>12</v>
+      </c>
+      <c r="E524">
+        <v>2026</v>
+      </c>
+      <c r="F524" s="3">
+        <f t="shared" si="9"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="525" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A525" t="s">
+        <v>0</v>
+      </c>
+      <c r="B525" t="s">
+        <v>17</v>
+      </c>
+      <c r="C525">
+        <v>310000000</v>
+      </c>
+      <c r="D525" s="4">
+        <v>1</v>
+      </c>
+      <c r="E525">
+        <v>2026</v>
+      </c>
+      <c r="F525" s="3">
+        <f t="shared" si="9"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="526" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A526" t="s">
+        <v>0</v>
+      </c>
+      <c r="B526" t="s">
+        <v>17</v>
+      </c>
+      <c r="C526">
+        <v>290000000</v>
+      </c>
+      <c r="D526" s="4">
+        <v>2</v>
+      </c>
+      <c r="E526">
+        <v>2026</v>
+      </c>
+      <c r="F526" s="3">
+        <f t="shared" si="9"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="527" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A527" t="s">
+        <v>0</v>
+      </c>
+      <c r="B527" t="s">
+        <v>17</v>
+      </c>
+      <c r="C527">
+        <v>210000000</v>
+      </c>
+      <c r="D527" s="4">
+        <v>3</v>
+      </c>
+      <c r="E527">
+        <v>2026</v>
+      </c>
+      <c r="F527" s="3">
+        <f t="shared" si="9"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="528" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A528" t="s">
+        <v>0</v>
+      </c>
+      <c r="B528" t="s">
+        <v>17</v>
+      </c>
+      <c r="C528">
+        <v>225000000</v>
+      </c>
+      <c r="D528" s="4">
+        <v>4</v>
+      </c>
+      <c r="E528">
+        <v>2026</v>
+      </c>
+      <c r="F528" s="3">
+        <f t="shared" si="9"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="529" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A529" t="s">
+        <v>0</v>
+      </c>
+      <c r="B529" t="s">
+        <v>17</v>
+      </c>
+      <c r="C529">
+        <v>230000000</v>
+      </c>
+      <c r="D529" s="4">
+        <v>5</v>
+      </c>
+      <c r="E529">
+        <v>2026</v>
+      </c>
+      <c r="F529" s="3">
+        <f t="shared" si="9"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="530" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A530" t="s">
+        <v>0</v>
+      </c>
+      <c r="B530" t="s">
+        <v>17</v>
+      </c>
+      <c r="C530">
+        <v>250000000</v>
+      </c>
+      <c r="D530" s="4">
+        <v>6</v>
+      </c>
+      <c r="E530">
+        <v>2026</v>
+      </c>
+      <c r="F530" s="3">
+        <f t="shared" si="9"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="531" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A531" t="s">
+        <v>0</v>
+      </c>
+      <c r="B531" t="s">
+        <v>17</v>
+      </c>
+      <c r="C531">
+        <v>330000000</v>
+      </c>
+      <c r="D531" s="4">
+        <v>7</v>
+      </c>
+      <c r="E531">
+        <v>2026</v>
+      </c>
+      <c r="F531" s="3">
+        <f t="shared" si="9"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="532" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A532" t="s">
+        <v>0</v>
+      </c>
+      <c r="B532" t="s">
+        <v>17</v>
+      </c>
+      <c r="C532">
+        <v>430000000</v>
+      </c>
+      <c r="D532" s="4">
+        <v>8</v>
+      </c>
+      <c r="E532">
+        <v>2026</v>
+      </c>
+      <c r="F532" s="3">
+        <f t="shared" si="9"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="533" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A533" t="s">
+        <v>0</v>
+      </c>
+      <c r="B533" t="s">
+        <v>17</v>
+      </c>
+      <c r="C533">
+        <v>205000000</v>
+      </c>
+      <c r="D533" s="4">
+        <v>9</v>
+      </c>
+      <c r="E533">
+        <v>2026</v>
+      </c>
+      <c r="F533" s="3">
+        <f t="shared" si="9"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="534" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A534" t="s">
+        <v>0</v>
+      </c>
+      <c r="B534" t="s">
+        <v>17</v>
+      </c>
+      <c r="C534">
+        <v>180000000</v>
+      </c>
+      <c r="D534" s="4">
+        <v>10</v>
+      </c>
+      <c r="E534">
+        <v>2026</v>
+      </c>
+      <c r="F534" s="3">
+        <f t="shared" si="9"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="535" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A535" t="s">
+        <v>0</v>
+      </c>
+      <c r="B535" t="s">
+        <v>17</v>
+      </c>
+      <c r="C535">
+        <v>340000000</v>
+      </c>
+      <c r="D535" s="4">
+        <v>11</v>
+      </c>
+      <c r="E535">
+        <v>2026</v>
+      </c>
+      <c r="F535" s="3">
+        <f t="shared" si="9"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="536" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A536" t="s">
+        <v>0</v>
+      </c>
+      <c r="B536" t="s">
+        <v>17</v>
+      </c>
+      <c r="C536">
+        <v>200000000</v>
+      </c>
+      <c r="D536" s="4">
+        <v>12</v>
+      </c>
+      <c r="E536">
+        <v>2026</v>
+      </c>
+      <c r="F536" s="3">
+        <f t="shared" si="9"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="537" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A537" t="s">
+        <v>0</v>
+      </c>
+      <c r="B537" t="s">
+        <v>18</v>
+      </c>
+      <c r="C537">
+        <v>240000000</v>
+      </c>
+      <c r="D537" s="4">
+        <v>1</v>
+      </c>
+      <c r="E537">
+        <v>2026</v>
+      </c>
+      <c r="F537" s="3">
+        <f t="shared" si="9"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="538" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A538" t="s">
+        <v>0</v>
+      </c>
+      <c r="B538" t="s">
+        <v>18</v>
+      </c>
+      <c r="C538">
+        <v>240000000</v>
+      </c>
+      <c r="D538" s="4">
+        <v>2</v>
+      </c>
+      <c r="E538">
+        <v>2026</v>
+      </c>
+      <c r="F538" s="3">
+        <f t="shared" si="9"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="539" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A539" t="s">
+        <v>0</v>
+      </c>
+      <c r="B539" t="s">
+        <v>18</v>
+      </c>
+      <c r="C539">
+        <v>200000000</v>
+      </c>
+      <c r="D539" s="4">
+        <v>3</v>
+      </c>
+      <c r="E539">
+        <v>2026</v>
+      </c>
+      <c r="F539" s="3">
+        <f t="shared" si="9"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="540" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A540" t="s">
+        <v>0</v>
+      </c>
+      <c r="B540" t="s">
+        <v>25</v>
+      </c>
+      <c r="C540">
+        <v>220000000</v>
+      </c>
+      <c r="D540" s="4">
+        <v>1</v>
+      </c>
+      <c r="E540">
+        <v>2026</v>
+      </c>
+      <c r="F540" s="3">
+        <f t="shared" ref="F540:F595" si="10">DATE(E540,D540,1)</f>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="541" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A541" t="s">
+        <v>0</v>
+      </c>
+      <c r="B541" t="s">
+        <v>25</v>
+      </c>
+      <c r="C541">
+        <v>210000000</v>
+      </c>
+      <c r="D541" s="4">
+        <v>2</v>
+      </c>
+      <c r="E541">
+        <v>2026</v>
+      </c>
+      <c r="F541" s="3">
+        <f t="shared" si="10"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="542" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A542" t="s">
+        <v>0</v>
+      </c>
+      <c r="B542" t="s">
+        <v>40</v>
+      </c>
+      <c r="C542">
+        <v>220000000</v>
+      </c>
+      <c r="D542" s="4">
+        <v>1</v>
+      </c>
+      <c r="E542">
+        <v>2026</v>
+      </c>
+      <c r="F542" s="3">
+        <f t="shared" si="10"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="543" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A543" t="s">
+        <v>0</v>
+      </c>
+      <c r="B543" t="s">
+        <v>40</v>
+      </c>
+      <c r="C543">
+        <v>210000000</v>
+      </c>
+      <c r="D543" s="4">
+        <v>2</v>
+      </c>
+      <c r="E543">
+        <v>2026</v>
+      </c>
+      <c r="F543" s="3">
+        <f t="shared" si="10"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="544" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A544" t="s">
+        <v>0</v>
+      </c>
+      <c r="B544" t="s">
+        <v>41</v>
+      </c>
+      <c r="C544">
+        <v>180000000</v>
+      </c>
+      <c r="D544" s="4">
+        <v>4</v>
+      </c>
+      <c r="E544">
+        <v>2026</v>
+      </c>
+      <c r="F544" s="3">
+        <f t="shared" si="10"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="545" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A545" t="s">
+        <v>0</v>
+      </c>
+      <c r="B545" t="s">
+        <v>41</v>
+      </c>
+      <c r="C545">
+        <v>200000000</v>
+      </c>
+      <c r="D545" s="4">
+        <v>5</v>
+      </c>
+      <c r="E545">
+        <v>2026</v>
+      </c>
+      <c r="F545" s="3">
+        <f t="shared" si="10"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="546" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A546" t="s">
+        <v>0</v>
+      </c>
+      <c r="B546" t="s">
+        <v>41</v>
+      </c>
+      <c r="C546">
+        <v>200000000</v>
+      </c>
+      <c r="D546" s="4">
+        <v>6</v>
+      </c>
+      <c r="E546">
+        <v>2026</v>
+      </c>
+      <c r="F546" s="3">
+        <f t="shared" si="10"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="547" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A547" t="s">
+        <v>0</v>
+      </c>
+      <c r="B547" t="s">
+        <v>41</v>
+      </c>
+      <c r="C547">
+        <v>250000000</v>
+      </c>
+      <c r="D547" s="4">
+        <v>7</v>
+      </c>
+      <c r="E547">
+        <v>2026</v>
+      </c>
+      <c r="F547" s="3">
+        <f t="shared" si="10"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="548" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A548" t="s">
+        <v>0</v>
+      </c>
+      <c r="B548" t="s">
+        <v>41</v>
+      </c>
+      <c r="C548">
+        <v>290000000</v>
+      </c>
+      <c r="D548" s="4">
+        <v>8</v>
+      </c>
+      <c r="E548">
+        <v>2026</v>
+      </c>
+      <c r="F548" s="3">
+        <f t="shared" si="10"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="549" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A549" t="s">
+        <v>0</v>
+      </c>
+      <c r="B549" t="s">
+        <v>41</v>
+      </c>
+      <c r="C549">
+        <v>200000000</v>
+      </c>
+      <c r="D549" s="4">
+        <v>9</v>
+      </c>
+      <c r="E549">
+        <v>2026</v>
+      </c>
+      <c r="F549" s="3">
+        <f t="shared" si="10"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="550" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A550" t="s">
+        <v>0</v>
+      </c>
+      <c r="B550" t="s">
+        <v>41</v>
+      </c>
+      <c r="C550">
+        <v>190000000</v>
+      </c>
+      <c r="D550" s="4">
+        <v>10</v>
+      </c>
+      <c r="E550">
+        <v>2026</v>
+      </c>
+      <c r="F550" s="3">
+        <f t="shared" si="10"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="551" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A551" t="s">
+        <v>0</v>
+      </c>
+      <c r="B551" t="s">
+        <v>41</v>
+      </c>
+      <c r="C551">
+        <v>260000000</v>
+      </c>
+      <c r="D551" s="4">
+        <v>11</v>
+      </c>
+      <c r="E551">
+        <v>2026</v>
+      </c>
+      <c r="F551" s="3">
+        <f t="shared" si="10"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="552" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A552" t="s">
+        <v>0</v>
+      </c>
+      <c r="B552" t="s">
+        <v>41</v>
+      </c>
+      <c r="C552">
+        <v>200000000</v>
+      </c>
+      <c r="D552" s="4">
+        <v>12</v>
+      </c>
+      <c r="E552">
+        <v>2026</v>
+      </c>
+      <c r="F552" s="3">
+        <f t="shared" si="10"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="553" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A553" t="s">
+        <v>0</v>
+      </c>
+      <c r="B553" t="s">
+        <v>42</v>
+      </c>
+      <c r="C553">
+        <v>180000000</v>
+      </c>
+      <c r="D553" s="4">
+        <v>4</v>
+      </c>
+      <c r="E553">
+        <v>2026</v>
+      </c>
+      <c r="F553" s="3">
+        <f t="shared" si="10"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="554" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A554" t="s">
+        <v>0</v>
+      </c>
+      <c r="B554" t="s">
+        <v>42</v>
+      </c>
+      <c r="C554">
+        <v>200000000</v>
+      </c>
+      <c r="D554" s="4">
+        <v>5</v>
+      </c>
+      <c r="E554">
+        <v>2026</v>
+      </c>
+      <c r="F554" s="3">
+        <f t="shared" si="10"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="555" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A555" t="s">
+        <v>0</v>
+      </c>
+      <c r="B555" t="s">
+        <v>42</v>
+      </c>
+      <c r="C555">
+        <v>200000000</v>
+      </c>
+      <c r="D555" s="4">
+        <v>6</v>
+      </c>
+      <c r="E555">
+        <v>2026</v>
+      </c>
+      <c r="F555" s="3">
+        <f t="shared" si="10"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="556" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A556" t="s">
+        <v>0</v>
+      </c>
+      <c r="B556" t="s">
+        <v>42</v>
+      </c>
+      <c r="C556">
+        <v>250000000</v>
+      </c>
+      <c r="D556" s="4">
+        <v>7</v>
+      </c>
+      <c r="E556">
+        <v>2026</v>
+      </c>
+      <c r="F556" s="3">
+        <f t="shared" si="10"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="557" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A557" t="s">
+        <v>0</v>
+      </c>
+      <c r="B557" t="s">
+        <v>42</v>
+      </c>
+      <c r="C557">
+        <v>290000000</v>
+      </c>
+      <c r="D557" s="4">
+        <v>8</v>
+      </c>
+      <c r="E557">
+        <v>2026</v>
+      </c>
+      <c r="F557" s="3">
+        <f t="shared" si="10"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="558" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A558" t="s">
+        <v>0</v>
+      </c>
+      <c r="B558" t="s">
+        <v>42</v>
+      </c>
+      <c r="C558">
+        <v>200000000</v>
+      </c>
+      <c r="D558" s="4">
+        <v>9</v>
+      </c>
+      <c r="E558">
+        <v>2026</v>
+      </c>
+      <c r="F558" s="3">
+        <f t="shared" si="10"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="559" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A559" t="s">
+        <v>0</v>
+      </c>
+      <c r="B559" t="s">
+        <v>42</v>
+      </c>
+      <c r="C559">
+        <v>190000000</v>
+      </c>
+      <c r="D559" s="4">
+        <v>10</v>
+      </c>
+      <c r="E559">
+        <v>2026</v>
+      </c>
+      <c r="F559" s="3">
+        <f t="shared" si="10"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="560" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A560" t="s">
+        <v>0</v>
+      </c>
+      <c r="B560" t="s">
+        <v>42</v>
+      </c>
+      <c r="C560">
+        <v>260000000</v>
+      </c>
+      <c r="D560" s="4">
+        <v>11</v>
+      </c>
+      <c r="E560">
+        <v>2026</v>
+      </c>
+      <c r="F560" s="3">
+        <f t="shared" si="10"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="561" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A561" t="s">
+        <v>0</v>
+      </c>
+      <c r="B561" t="s">
+        <v>42</v>
+      </c>
+      <c r="C561">
+        <v>200000000</v>
+      </c>
+      <c r="D561" s="4">
+        <v>12</v>
+      </c>
+      <c r="E561">
+        <v>2026</v>
+      </c>
+      <c r="F561" s="3">
+        <f t="shared" si="10"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="562" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A562" t="s">
+        <v>0</v>
+      </c>
+      <c r="B562" t="s">
+        <v>43</v>
+      </c>
+      <c r="C562">
+        <v>180000000</v>
+      </c>
+      <c r="D562" s="4">
+        <v>5</v>
+      </c>
+      <c r="E562">
+        <v>2026</v>
+      </c>
+      <c r="F562" s="3">
+        <f t="shared" si="10"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="563" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A563" t="s">
+        <v>0</v>
+      </c>
+      <c r="B563" t="s">
+        <v>43</v>
+      </c>
+      <c r="C563">
+        <v>200000000</v>
+      </c>
+      <c r="D563" s="4">
+        <v>6</v>
+      </c>
+      <c r="E563">
+        <v>2026</v>
+      </c>
+      <c r="F563" s="3">
+        <f t="shared" si="10"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="564" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A564" t="s">
+        <v>0</v>
+      </c>
+      <c r="B564" t="s">
+        <v>43</v>
+      </c>
+      <c r="C564">
+        <v>250000000</v>
+      </c>
+      <c r="D564" s="4">
+        <v>7</v>
+      </c>
+      <c r="E564">
+        <v>2026</v>
+      </c>
+      <c r="F564" s="3">
+        <f t="shared" si="10"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="565" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A565" t="s">
+        <v>0</v>
+      </c>
+      <c r="B565" t="s">
+        <v>43</v>
+      </c>
+      <c r="C565">
+        <v>290000000</v>
+      </c>
+      <c r="D565" s="4">
+        <v>8</v>
+      </c>
+      <c r="E565">
+        <v>2026</v>
+      </c>
+      <c r="F565" s="3">
+        <f t="shared" si="10"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="566" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A566" t="s">
+        <v>0</v>
+      </c>
+      <c r="B566" t="s">
+        <v>43</v>
+      </c>
+      <c r="C566">
+        <v>200000000</v>
+      </c>
+      <c r="D566" s="4">
+        <v>9</v>
+      </c>
+      <c r="E566">
+        <v>2026</v>
+      </c>
+      <c r="F566" s="3">
+        <f t="shared" si="10"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="567" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A567" t="s">
+        <v>0</v>
+      </c>
+      <c r="B567" t="s">
+        <v>43</v>
+      </c>
+      <c r="C567">
+        <v>190000000</v>
+      </c>
+      <c r="D567" s="4">
+        <v>10</v>
+      </c>
+      <c r="E567">
+        <v>2026</v>
+      </c>
+      <c r="F567" s="3">
+        <f t="shared" si="10"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="568" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A568" t="s">
+        <v>0</v>
+      </c>
+      <c r="B568" t="s">
+        <v>43</v>
+      </c>
+      <c r="C568">
+        <v>260000000</v>
+      </c>
+      <c r="D568" s="4">
+        <v>11</v>
+      </c>
+      <c r="E568">
+        <v>2026</v>
+      </c>
+      <c r="F568" s="3">
+        <f t="shared" si="10"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="569" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A569" t="s">
+        <v>0</v>
+      </c>
+      <c r="B569" t="s">
+        <v>43</v>
+      </c>
+      <c r="C569">
+        <v>200000000</v>
+      </c>
+      <c r="D569" s="4">
+        <v>12</v>
+      </c>
+      <c r="E569">
+        <v>2026</v>
+      </c>
+      <c r="F569" s="3">
+        <f t="shared" si="10"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="570" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A570" t="s">
+        <v>0</v>
+      </c>
+      <c r="B570" t="s">
+        <v>44</v>
+      </c>
+      <c r="C570">
+        <v>180000000</v>
+      </c>
+      <c r="D570" s="4">
+        <v>6</v>
+      </c>
+      <c r="E570">
+        <v>2026</v>
+      </c>
+      <c r="F570" s="3">
+        <f t="shared" si="10"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="571" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A571" t="s">
+        <v>0</v>
+      </c>
+      <c r="B571" t="s">
+        <v>44</v>
+      </c>
+      <c r="C571">
+        <v>200000000</v>
+      </c>
+      <c r="D571" s="4">
+        <v>7</v>
+      </c>
+      <c r="E571">
+        <v>2026</v>
+      </c>
+      <c r="F571" s="3">
+        <f t="shared" si="10"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="572" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A572" t="s">
+        <v>0</v>
+      </c>
+      <c r="B572" t="s">
+        <v>44</v>
+      </c>
+      <c r="C572">
+        <v>260000000</v>
+      </c>
+      <c r="D572" s="4">
+        <v>8</v>
+      </c>
+      <c r="E572">
+        <v>2026</v>
+      </c>
+      <c r="F572" s="3">
+        <f t="shared" si="10"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="573" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A573" t="s">
+        <v>0</v>
+      </c>
+      <c r="B573" t="s">
+        <v>44</v>
+      </c>
+      <c r="C573">
+        <v>200000000</v>
+      </c>
+      <c r="D573" s="4">
+        <v>9</v>
+      </c>
+      <c r="E573">
+        <v>2026</v>
+      </c>
+      <c r="F573" s="3">
+        <f t="shared" si="10"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="574" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A574" t="s">
+        <v>0</v>
+      </c>
+      <c r="B574" t="s">
+        <v>44</v>
+      </c>
+      <c r="C574">
+        <v>190000000</v>
+      </c>
+      <c r="D574" s="4">
+        <v>10</v>
+      </c>
+      <c r="E574">
+        <v>2026</v>
+      </c>
+      <c r="F574" s="3">
+        <f t="shared" si="10"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="575" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A575" t="s">
+        <v>0</v>
+      </c>
+      <c r="B575" t="s">
+        <v>44</v>
+      </c>
+      <c r="C575">
+        <v>260000000</v>
+      </c>
+      <c r="D575" s="4">
+        <v>11</v>
+      </c>
+      <c r="E575">
+        <v>2026</v>
+      </c>
+      <c r="F575" s="3">
+        <f t="shared" si="10"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="576" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A576" t="s">
+        <v>0</v>
+      </c>
+      <c r="B576" t="s">
+        <v>44</v>
+      </c>
+      <c r="C576">
+        <v>200000000</v>
+      </c>
+      <c r="D576" s="4">
+        <v>12</v>
+      </c>
+      <c r="E576">
+        <v>2026</v>
+      </c>
+      <c r="F576" s="3">
+        <f t="shared" si="10"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="577" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A577" t="s">
+        <v>0</v>
+      </c>
+      <c r="B577" t="s">
+        <v>45</v>
+      </c>
+      <c r="C577">
+        <v>180000000</v>
+      </c>
+      <c r="D577" s="4">
+        <v>9</v>
+      </c>
+      <c r="E577">
+        <v>2026</v>
+      </c>
+      <c r="F577" s="3">
+        <f t="shared" si="10"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="578" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A578" t="s">
+        <v>0</v>
+      </c>
+      <c r="B578" t="s">
+        <v>45</v>
+      </c>
+      <c r="C578">
+        <v>190000000</v>
+      </c>
+      <c r="D578" s="4">
+        <v>10</v>
+      </c>
+      <c r="E578">
+        <v>2026</v>
+      </c>
+      <c r="F578" s="3">
+        <f t="shared" si="10"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="579" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A579" t="s">
+        <v>0</v>
+      </c>
+      <c r="B579" t="s">
+        <v>45</v>
+      </c>
+      <c r="C579">
+        <v>240000000</v>
+      </c>
+      <c r="D579" s="4">
+        <v>11</v>
+      </c>
+      <c r="E579">
+        <v>2026</v>
+      </c>
+      <c r="F579" s="3">
+        <f t="shared" si="10"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="580" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A580" t="s">
+        <v>0</v>
+      </c>
+      <c r="B580" t="s">
+        <v>45</v>
+      </c>
+      <c r="C580">
+        <v>200000000</v>
+      </c>
+      <c r="D580" s="4">
+        <v>12</v>
+      </c>
+      <c r="E580">
+        <v>2026</v>
+      </c>
+      <c r="F580" s="3">
+        <f t="shared" si="10"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="581" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A581" t="s">
+        <v>0</v>
+      </c>
+      <c r="B581" t="s">
+        <v>46</v>
+      </c>
+      <c r="C581">
+        <v>180000000</v>
+      </c>
+      <c r="D581" s="4">
+        <v>10</v>
+      </c>
+      <c r="E581">
+        <v>2026</v>
+      </c>
+      <c r="F581" s="3">
+        <f t="shared" si="10"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="582" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A582" t="s">
+        <v>0</v>
+      </c>
+      <c r="B582" t="s">
+        <v>46</v>
+      </c>
+      <c r="C582">
+        <v>220000000</v>
+      </c>
+      <c r="D582" s="4">
+        <v>11</v>
+      </c>
+      <c r="E582">
+        <v>2026</v>
+      </c>
+      <c r="F582" s="3">
+        <f t="shared" si="10"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="583" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A583" t="s">
+        <v>0</v>
+      </c>
+      <c r="B583" t="s">
+        <v>46</v>
+      </c>
+      <c r="C583">
+        <v>200000000</v>
+      </c>
+      <c r="D583" s="4">
+        <v>12</v>
+      </c>
+      <c r="E583">
+        <v>2026</v>
+      </c>
+      <c r="F583" s="3">
+        <f t="shared" si="10"/>
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="584" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A584" t="s">
+        <v>1</v>
+      </c>
+      <c r="B584" t="s">
+        <v>1</v>
+      </c>
+      <c r="C584">
+        <v>2500000000</v>
+      </c>
+      <c r="D584" s="4">
+        <v>1</v>
+      </c>
+      <c r="E584">
+        <v>2026</v>
+      </c>
+      <c r="F584" s="3">
+        <f t="shared" si="10"/>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="585" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A585" t="s">
+        <v>1</v>
+      </c>
+      <c r="B585" t="s">
+        <v>1</v>
+      </c>
+      <c r="C585">
+        <v>1300000000</v>
+      </c>
+      <c r="D585" s="4">
+        <v>2</v>
+      </c>
+      <c r="E585">
+        <v>2026</v>
+      </c>
+      <c r="F585" s="3">
+        <f t="shared" si="10"/>
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="586" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A586" t="s">
+        <v>1</v>
+      </c>
+      <c r="B586" t="s">
+        <v>1</v>
+      </c>
+      <c r="C586">
+        <v>1800000000</v>
+      </c>
+      <c r="D586" s="4">
+        <v>3</v>
+      </c>
+      <c r="E586">
+        <v>2026</v>
+      </c>
+      <c r="F586" s="3">
+        <f t="shared" si="10"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="587" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A587" t="s">
+        <v>1</v>
+      </c>
+      <c r="B587" t="s">
+        <v>1</v>
+      </c>
+      <c r="C587">
+        <v>1800000000</v>
+      </c>
+      <c r="D587" s="4">
+        <v>4</v>
+      </c>
+      <c r="E587">
+        <v>2026</v>
+      </c>
+      <c r="F587" s="3">
+        <f t="shared" si="10"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="588" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A588" t="s">
+        <v>1</v>
+      </c>
+      <c r="B588" t="s">
+        <v>1</v>
+      </c>
+      <c r="C588">
+        <v>1900000000</v>
+      </c>
+      <c r="D588" s="4">
+        <v>5</v>
+      </c>
+      <c r="E588">
+        <v>2026</v>
+      </c>
+      <c r="F588" s="3">
+        <f t="shared" si="10"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="589" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A589" t="s">
+        <v>1</v>
+      </c>
+      <c r="B589" t="s">
+        <v>1</v>
+      </c>
+      <c r="C589">
+        <v>2000000000</v>
+      </c>
+      <c r="D589" s="4">
+        <v>6</v>
+      </c>
+      <c r="E589">
+        <v>2026</v>
+      </c>
+      <c r="F589" s="3">
+        <f t="shared" si="10"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="590" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A590" t="s">
+        <v>1</v>
+      </c>
+      <c r="B590" t="s">
+        <v>1</v>
+      </c>
+      <c r="C590">
+        <v>2900000000</v>
+      </c>
+      <c r="D590" s="4">
+        <v>7</v>
+      </c>
+      <c r="E590">
+        <v>2026</v>
+      </c>
+      <c r="F590" s="3">
+        <f t="shared" si="10"/>
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="591" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A591" t="s">
+        <v>1</v>
+      </c>
+      <c r="B591" t="s">
+        <v>1</v>
+      </c>
+      <c r="C591">
+        <v>4500000000</v>
+      </c>
+      <c r="D591" s="4">
+        <v>8</v>
+      </c>
+      <c r="E591">
+        <v>2026</v>
+      </c>
+      <c r="F591" s="3">
+        <f t="shared" si="10"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="592" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A592" t="s">
+        <v>1</v>
+      </c>
+      <c r="B592" t="s">
+        <v>1</v>
+      </c>
+      <c r="C592">
+        <v>2700000000</v>
+      </c>
+      <c r="D592" s="4">
+        <v>9</v>
+      </c>
+      <c r="E592">
+        <v>2026</v>
+      </c>
+      <c r="F592" s="3">
+        <f t="shared" si="10"/>
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="593" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A593" t="s">
+        <v>1</v>
+      </c>
+      <c r="B593" t="s">
+        <v>1</v>
+      </c>
+      <c r="C593">
+        <v>2300000000</v>
+      </c>
+      <c r="D593" s="4">
+        <v>10</v>
+      </c>
+      <c r="E593">
+        <v>2026</v>
+      </c>
+      <c r="F593" s="3">
+        <f t="shared" si="10"/>
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="594" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A594" t="s">
+        <v>1</v>
+      </c>
+      <c r="B594" t="s">
+        <v>1</v>
+      </c>
+      <c r="C594">
+        <v>2300000000</v>
+      </c>
+      <c r="D594" s="4">
+        <v>11</v>
+      </c>
+      <c r="E594">
+        <v>2026</v>
+      </c>
+      <c r="F594" s="3">
+        <f t="shared" si="10"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="595" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A595" t="s">
+        <v>1</v>
+      </c>
+      <c r="B595" t="s">
+        <v>1</v>
+      </c>
+      <c r="C595">
+        <v>2000000000</v>
+      </c>
+      <c r="D595" s="4">
+        <v>12</v>
+      </c>
+      <c r="E595">
+        <v>2026</v>
+      </c>
+      <c r="F595" s="3">
+        <f t="shared" si="10"/>
+        <v>46357</v>
       </c>
     </row>
   </sheetData>

--- a/table_adjust.xlsx
+++ b/table_adjust.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8268aba086fcb9b8/KDA_Trinh Võ/KDA data/PYTHON_OPERATION/ma_shondo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{753EE1B0-0A9A-452A-BCE9-F8BF0F505AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{293CD153-6603-462B-B137-55CAC8FB3D2E}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{753EE1B0-0A9A-452A-BCE9-F8BF0F505AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C6AC4BF-80B6-4E8D-98F5-F0E61F8523DB}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F1D8C3B-B510-45F3-82FB-DF857C4D318C}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="46">
   <si>
     <t>KDC</t>
   </si>
@@ -162,9 +162,6 @@
   </si>
   <si>
     <t>FB/INS/ZL/NB</t>
-  </si>
-  <si>
-    <t>101AEONHP</t>
   </si>
   <si>
     <t>CH (thay BD)</t>
@@ -11897,7 +11894,7 @@
         <v>0</v>
       </c>
       <c r="B542" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C542">
         <v>220000000</v>
@@ -11918,7 +11915,7 @@
         <v>0</v>
       </c>
       <c r="B543" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C543">
         <v>210000000</v>
@@ -11939,7 +11936,7 @@
         <v>0</v>
       </c>
       <c r="B544" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C544">
         <v>180000000</v>
@@ -11960,7 +11957,7 @@
         <v>0</v>
       </c>
       <c r="B545" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C545">
         <v>200000000</v>
@@ -11981,7 +11978,7 @@
         <v>0</v>
       </c>
       <c r="B546" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C546">
         <v>200000000</v>
@@ -12002,7 +11999,7 @@
         <v>0</v>
       </c>
       <c r="B547" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C547">
         <v>250000000</v>
@@ -12023,7 +12020,7 @@
         <v>0</v>
       </c>
       <c r="B548" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C548">
         <v>290000000</v>
@@ -12044,7 +12041,7 @@
         <v>0</v>
       </c>
       <c r="B549" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C549">
         <v>200000000</v>
@@ -12065,7 +12062,7 @@
         <v>0</v>
       </c>
       <c r="B550" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C550">
         <v>190000000</v>
@@ -12086,7 +12083,7 @@
         <v>0</v>
       </c>
       <c r="B551" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C551">
         <v>260000000</v>
@@ -12107,7 +12104,7 @@
         <v>0</v>
       </c>
       <c r="B552" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C552">
         <v>200000000</v>
@@ -12128,7 +12125,7 @@
         <v>0</v>
       </c>
       <c r="B553" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C553">
         <v>180000000</v>
@@ -12149,7 +12146,7 @@
         <v>0</v>
       </c>
       <c r="B554" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C554">
         <v>200000000</v>
@@ -12170,7 +12167,7 @@
         <v>0</v>
       </c>
       <c r="B555" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C555">
         <v>200000000</v>
@@ -12191,7 +12188,7 @@
         <v>0</v>
       </c>
       <c r="B556" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C556">
         <v>250000000</v>
@@ -12212,7 +12209,7 @@
         <v>0</v>
       </c>
       <c r="B557" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C557">
         <v>290000000</v>
@@ -12233,7 +12230,7 @@
         <v>0</v>
       </c>
       <c r="B558" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C558">
         <v>200000000</v>
@@ -12254,7 +12251,7 @@
         <v>0</v>
       </c>
       <c r="B559" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C559">
         <v>190000000</v>
@@ -12275,7 +12272,7 @@
         <v>0</v>
       </c>
       <c r="B560" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C560">
         <v>260000000</v>
@@ -12296,7 +12293,7 @@
         <v>0</v>
       </c>
       <c r="B561" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C561">
         <v>200000000</v>
@@ -12317,7 +12314,7 @@
         <v>0</v>
       </c>
       <c r="B562" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C562">
         <v>180000000</v>
@@ -12338,7 +12335,7 @@
         <v>0</v>
       </c>
       <c r="B563" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C563">
         <v>200000000</v>
@@ -12359,7 +12356,7 @@
         <v>0</v>
       </c>
       <c r="B564" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C564">
         <v>250000000</v>
@@ -12380,7 +12377,7 @@
         <v>0</v>
       </c>
       <c r="B565" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C565">
         <v>290000000</v>
@@ -12401,7 +12398,7 @@
         <v>0</v>
       </c>
       <c r="B566" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C566">
         <v>200000000</v>
@@ -12422,7 +12419,7 @@
         <v>0</v>
       </c>
       <c r="B567" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C567">
         <v>190000000</v>
@@ -12443,7 +12440,7 @@
         <v>0</v>
       </c>
       <c r="B568" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C568">
         <v>260000000</v>
@@ -12464,7 +12461,7 @@
         <v>0</v>
       </c>
       <c r="B569" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C569">
         <v>200000000</v>
@@ -12485,7 +12482,7 @@
         <v>0</v>
       </c>
       <c r="B570" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C570">
         <v>180000000</v>
@@ -12506,7 +12503,7 @@
         <v>0</v>
       </c>
       <c r="B571" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C571">
         <v>200000000</v>
@@ -12527,7 +12524,7 @@
         <v>0</v>
       </c>
       <c r="B572" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C572">
         <v>260000000</v>
@@ -12548,7 +12545,7 @@
         <v>0</v>
       </c>
       <c r="B573" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C573">
         <v>200000000</v>
@@ -12569,7 +12566,7 @@
         <v>0</v>
       </c>
       <c r="B574" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C574">
         <v>190000000</v>
@@ -12590,7 +12587,7 @@
         <v>0</v>
       </c>
       <c r="B575" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C575">
         <v>260000000</v>
@@ -12611,7 +12608,7 @@
         <v>0</v>
       </c>
       <c r="B576" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C576">
         <v>200000000</v>
@@ -12632,7 +12629,7 @@
         <v>0</v>
       </c>
       <c r="B577" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C577">
         <v>180000000</v>
@@ -12653,7 +12650,7 @@
         <v>0</v>
       </c>
       <c r="B578" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C578">
         <v>190000000</v>
@@ -12674,7 +12671,7 @@
         <v>0</v>
       </c>
       <c r="B579" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C579">
         <v>240000000</v>
@@ -12695,7 +12692,7 @@
         <v>0</v>
       </c>
       <c r="B580" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C580">
         <v>200000000</v>
@@ -12716,7 +12713,7 @@
         <v>0</v>
       </c>
       <c r="B581" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C581">
         <v>180000000</v>
@@ -12737,7 +12734,7 @@
         <v>0</v>
       </c>
       <c r="B582" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C582">
         <v>220000000</v>
@@ -12758,7 +12755,7 @@
         <v>0</v>
       </c>
       <c r="B583" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C583">
         <v>200000000</v>

--- a/table_adjust.xlsx
+++ b/table_adjust.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8268aba086fcb9b8/KDA_Trinh Võ/KDA data/PYTHON_OPERATION/ma_shondo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="8_{753EE1B0-0A9A-452A-BCE9-F8BF0F505AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C6AC4BF-80B6-4E8D-98F5-F0E61F8523DB}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="8_{753EE1B0-0A9A-452A-BCE9-F8BF0F505AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E613A4FF-350F-47DA-84A1-AB6A6735EAB2}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F1D8C3B-B510-45F3-82FB-DF857C4D318C}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="kpi" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">kpi!$A$1:$F$595</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">kpi!$A$1:$F$596</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="45">
   <si>
     <t>KDC</t>
   </si>
@@ -96,9 +96,6 @@
   </si>
   <si>
     <t>357AEONBINHTAN</t>
-  </si>
-  <si>
-    <t>358AEONBINHDUONG</t>
   </si>
   <si>
     <t>101AEONHAIPHONG</t>
@@ -164,9 +161,6 @@
     <t>FB/INS/ZL/NB</t>
   </si>
   <si>
-    <t>CH (thay BD)</t>
-  </si>
-  <si>
     <t>CH MỚI 1</t>
   </si>
   <si>
@@ -180,6 +174,9 @@
   </si>
   <si>
     <t>CH MỚI 5</t>
+  </si>
+  <si>
+    <t>358YERSINBD</t>
   </si>
 </sst>
 </file>
@@ -560,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CECFDCC4-BC95-4EB9-8D2E-CA772917AEFE}">
-  <dimension ref="A1:F595"/>
+  <dimension ref="A1:F596"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="20.08203125" bestFit="1" customWidth="1"/>
@@ -570,22 +567,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -866,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1">
         <v>221518511</v>
@@ -887,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" s="1">
         <v>71026100</v>
@@ -908,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" s="1">
         <v>225838750</v>
@@ -929,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" s="1">
         <v>234776500</v>
@@ -950,7 +947,7 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" s="1">
         <v>110136200</v>
@@ -971,7 +968,7 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" s="1">
         <v>162703700</v>
@@ -992,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" s="1">
         <v>152124150</v>
@@ -1013,7 +1010,7 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22" s="1">
         <v>92974600</v>
@@ -1034,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23" s="1">
         <v>127224920</v>
@@ -1055,7 +1052,7 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24" s="1">
         <v>130317850</v>
@@ -1349,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C38" s="1">
         <v>88960050</v>
@@ -1370,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C39" s="1">
         <v>48351300</v>
@@ -1391,7 +1388,7 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C40" s="1">
         <v>95933850</v>
@@ -1412,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C41" s="1">
         <v>91374225</v>
@@ -1433,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C42" s="1">
         <v>31895000</v>
@@ -1454,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C43" s="1">
         <v>94986000</v>
@@ -1475,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C44" s="1">
         <v>71239351</v>
@@ -1496,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C45" s="1">
         <v>40676200</v>
@@ -1517,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C46" s="1">
         <v>100764550</v>
@@ -1538,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C47" s="1">
         <v>96572800</v>
@@ -1832,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C61" s="1">
         <v>86335700</v>
@@ -1853,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C62" s="1">
         <v>88460550</v>
@@ -1874,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D63">
         <v>3</v>
@@ -1892,7 +1889,7 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C64" s="1">
         <v>121367950</v>
@@ -1913,7 +1910,7 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C65" s="1">
         <v>55720650</v>
@@ -1934,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C66" s="1">
         <v>62787500</v>
@@ -1955,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C67" s="1">
         <v>68891500</v>
@@ -1976,7 +1973,7 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C68" s="1">
         <v>51617900</v>
@@ -1997,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C69" s="1">
         <v>95364700</v>
@@ -2018,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C70" s="1">
         <v>97193333</v>
@@ -2039,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C71" s="1">
         <v>280000000</v>
@@ -2060,7 +2057,7 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C72" s="1">
         <v>200000000</v>
@@ -2081,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C73" s="1">
         <v>200000000</v>
@@ -2102,7 +2099,7 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C74" s="1">
         <v>200000000</v>
@@ -2123,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C75" s="1">
         <v>200000000</v>
@@ -2144,7 +2141,7 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C76" s="1">
         <v>200000000</v>
@@ -2165,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C77" s="1">
         <v>280000000</v>
@@ -2186,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C78" s="1">
         <v>200000000</v>
@@ -2207,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C79" s="1">
         <v>200000000</v>
@@ -2228,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C80" s="1">
         <v>200000000</v>
@@ -2249,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C81" s="1">
         <v>200000000</v>
@@ -2270,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C82" s="1">
         <v>200000000</v>
@@ -2291,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C83">
         <v>150000000</v>
@@ -2942,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C114">
         <v>200000000</v>
@@ -2963,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C115">
         <v>170000000</v>
@@ -2984,7 +2981,7 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C116" s="1">
         <v>200000000</v>
@@ -3005,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C117" s="1">
         <v>200000000</v>
@@ -3026,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C118" s="1">
         <v>220000000</v>
@@ -3047,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C119" s="1">
         <v>200000000</v>
@@ -3320,7 +3317,7 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C132" s="1">
         <v>180000000</v>
@@ -3341,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C133" s="1">
         <v>170000000</v>
@@ -3866,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="B158" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C158" s="1">
         <v>150000000</v>
@@ -3887,7 +3884,7 @@
         <v>0</v>
       </c>
       <c r="B159" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C159" s="1">
         <v>140000000</v>
@@ -4034,7 +4031,7 @@
         <v>0</v>
       </c>
       <c r="B166" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C166" s="1">
         <v>150000000</v>
@@ -4055,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="B167" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C167" s="1">
         <v>140000000</v>
@@ -4076,7 +4073,7 @@
         <v>0</v>
       </c>
       <c r="B168" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C168" s="1">
         <v>150000000</v>
@@ -4097,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="B169" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C169" s="1">
         <v>170000000</v>
@@ -4118,7 +4115,7 @@
         <v>0</v>
       </c>
       <c r="B170" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C170" s="1">
         <v>210000000</v>
@@ -4139,7 +4136,7 @@
         <v>0</v>
       </c>
       <c r="B171" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C171" s="1">
         <v>200000000</v>
@@ -4286,7 +4283,7 @@
         <v>0</v>
       </c>
       <c r="B178" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C178">
         <v>280000000</v>
@@ -4307,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="B179" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C179">
         <v>220000000</v>
@@ -4328,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="B180" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C180">
         <v>220000000</v>
@@ -4349,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="B181" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C181">
         <v>250000000</v>
@@ -4370,7 +4367,7 @@
         <v>0</v>
       </c>
       <c r="B182" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C182">
         <v>280000000</v>
@@ -4391,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="B183" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C183" s="1">
         <v>250000000</v>
@@ -4601,7 +4598,7 @@
         <v>2</v>
       </c>
       <c r="B193" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C193" s="1">
         <v>85948400</v>
@@ -4622,7 +4619,7 @@
         <v>2</v>
       </c>
       <c r="B194" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C194" s="1">
         <v>61652750</v>
@@ -4643,7 +4640,7 @@
         <v>2</v>
       </c>
       <c r="B195" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C195" s="1">
         <v>222559500</v>
@@ -4664,7 +4661,7 @@
         <v>2</v>
       </c>
       <c r="B196" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C196">
         <v>156030000</v>
@@ -4685,7 +4682,7 @@
         <v>2</v>
       </c>
       <c r="B197" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C197">
         <v>163625000</v>
@@ -4706,7 +4703,7 @@
         <v>2</v>
       </c>
       <c r="B198" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C198">
         <v>163625000</v>
@@ -4727,7 +4724,7 @@
         <v>2</v>
       </c>
       <c r="B199" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C199">
         <v>389600000</v>
@@ -4748,7 +4745,7 @@
         <v>2</v>
       </c>
       <c r="B200" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C200">
         <v>467550000</v>
@@ -4769,7 +4766,7 @@
         <v>2</v>
       </c>
       <c r="B201" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C201">
         <v>259750000</v>
@@ -4790,7 +4787,7 @@
         <v>2</v>
       </c>
       <c r="B202" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C202" s="1">
         <v>109003800</v>
@@ -4811,7 +4808,7 @@
         <v>2</v>
       </c>
       <c r="B203" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C203" s="1">
         <v>43255250</v>
@@ -4832,7 +4829,7 @@
         <v>2</v>
       </c>
       <c r="B204" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C204" s="1">
         <v>67192300</v>
@@ -4853,7 +4850,7 @@
         <v>2</v>
       </c>
       <c r="B205" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C205">
         <v>222900000</v>
@@ -4874,7 +4871,7 @@
         <v>2</v>
       </c>
       <c r="B206" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C206">
         <v>233750000</v>
@@ -4895,7 +4892,7 @@
         <v>2</v>
       </c>
       <c r="B207" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C207">
         <v>233750000</v>
@@ -4916,7 +4913,7 @@
         <v>2</v>
       </c>
       <c r="B208" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C208">
         <v>623360000</v>
@@ -4937,7 +4934,7 @@
         <v>2</v>
       </c>
       <c r="B209" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C209">
         <v>748080000</v>
@@ -4958,7 +4955,7 @@
         <v>2</v>
       </c>
       <c r="B210" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C210">
         <v>415600000</v>
@@ -4979,7 +4976,7 @@
         <v>2</v>
       </c>
       <c r="B211" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C211" s="1">
         <v>1795934668</v>
@@ -5000,7 +4997,7 @@
         <v>2</v>
       </c>
       <c r="B212" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C212" s="1">
         <v>1455532361</v>
@@ -5021,7 +5018,7 @@
         <v>2</v>
       </c>
       <c r="B213" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C213" s="1">
         <v>1029865752</v>
@@ -5042,7 +5039,7 @@
         <v>2</v>
       </c>
       <c r="B214" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C214">
         <v>2072970000</v>
@@ -5063,7 +5060,7 @@
         <v>2</v>
       </c>
       <c r="B215" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C215">
         <v>2173875000</v>
@@ -5084,7 +5081,7 @@
         <v>2</v>
       </c>
       <c r="B216" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C216">
         <v>2173875000</v>
@@ -5105,7 +5102,7 @@
         <v>2</v>
       </c>
       <c r="B217" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C217">
         <v>3662240000</v>
@@ -5126,7 +5123,7 @@
         <v>2</v>
       </c>
       <c r="B218" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C218">
         <v>4394970000</v>
@@ -5147,7 +5144,7 @@
         <v>2</v>
       </c>
       <c r="B219" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C219">
         <v>2441650000</v>
@@ -5168,7 +5165,7 @@
         <v>2</v>
       </c>
       <c r="B220" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C220" s="1">
         <v>902886867</v>
@@ -5189,7 +5186,7 @@
         <v>2</v>
       </c>
       <c r="B221" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C221" s="1">
         <v>1288909864</v>
@@ -5210,7 +5207,7 @@
         <v>2</v>
       </c>
       <c r="B222" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C222" s="1">
         <v>1171700160</v>
@@ -5231,7 +5228,7 @@
         <v>2</v>
       </c>
       <c r="B223" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C223">
         <v>2006100000</v>
@@ -5252,7 +5249,7 @@
         <v>2</v>
       </c>
       <c r="B224" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C224">
         <v>2103750000</v>
@@ -5273,7 +5270,7 @@
         <v>2</v>
       </c>
       <c r="B225" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C225">
         <v>2103750000</v>
@@ -5294,7 +5291,7 @@
         <v>2</v>
       </c>
       <c r="B226" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C226">
         <v>3116800000</v>
@@ -5315,7 +5312,7 @@
         <v>2</v>
       </c>
       <c r="B227" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C227">
         <v>3740400000</v>
@@ -5336,7 +5333,7 @@
         <v>2</v>
       </c>
       <c r="B228" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C228">
         <v>2078000000</v>
@@ -5357,7 +5354,7 @@
         <v>3</v>
       </c>
       <c r="B229" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D229">
         <v>1</v>
@@ -5375,7 +5372,7 @@
         <v>3</v>
       </c>
       <c r="B230" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D230">
         <v>2</v>
@@ -5393,7 +5390,7 @@
         <v>3</v>
       </c>
       <c r="B231" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D231">
         <v>3</v>
@@ -5411,7 +5408,7 @@
         <v>3</v>
       </c>
       <c r="B232" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D232">
         <v>4</v>
@@ -5429,7 +5426,7 @@
         <v>3</v>
       </c>
       <c r="B233" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D233">
         <v>5</v>
@@ -5447,7 +5444,7 @@
         <v>3</v>
       </c>
       <c r="B234" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D234">
         <v>6</v>
@@ -5465,7 +5462,7 @@
         <v>3</v>
       </c>
       <c r="B235" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C235" s="1">
         <v>100000000</v>
@@ -5486,7 +5483,7 @@
         <v>3</v>
       </c>
       <c r="B236" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C236" s="1">
         <v>400000000</v>
@@ -5507,7 +5504,7 @@
         <v>3</v>
       </c>
       <c r="B237" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C237" s="1">
         <v>500000000</v>
@@ -5528,7 +5525,7 @@
         <v>4</v>
       </c>
       <c r="B238" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D238">
         <v>1</v>
@@ -5546,7 +5543,7 @@
         <v>4</v>
       </c>
       <c r="B239" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D239">
         <v>2</v>
@@ -5564,7 +5561,7 @@
         <v>4</v>
       </c>
       <c r="B240" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D240">
         <v>3</v>
@@ -5582,7 +5579,7 @@
         <v>4</v>
       </c>
       <c r="B241" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D241">
         <v>4</v>
@@ -5600,7 +5597,7 @@
         <v>4</v>
       </c>
       <c r="B242" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D242">
         <v>5</v>
@@ -5618,7 +5615,7 @@
         <v>4</v>
       </c>
       <c r="B243" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D243">
         <v>6</v>
@@ -5636,7 +5633,7 @@
         <v>4</v>
       </c>
       <c r="B244" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C244" s="1">
         <v>2000000000</v>
@@ -5657,7 +5654,7 @@
         <v>4</v>
       </c>
       <c r="B245" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C245" s="1">
         <v>4000000000</v>
@@ -5678,7 +5675,7 @@
         <v>4</v>
       </c>
       <c r="B246" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C246" s="1">
         <v>2000000000</v>
@@ -5972,7 +5969,7 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C260">
         <v>250000000</v>
@@ -5993,7 +5990,7 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C261">
         <v>200000000</v>
@@ -6014,7 +6011,7 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C262">
         <v>200000000</v>
@@ -6035,7 +6032,7 @@
         <v>0</v>
       </c>
       <c r="B263" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C263">
         <v>200000000</v>
@@ -6056,7 +6053,7 @@
         <v>0</v>
       </c>
       <c r="B264" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C264">
         <v>200000000</v>
@@ -6350,7 +6347,7 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C278">
         <v>280000000</v>
@@ -6371,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="B279" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C279">
         <v>200000000</v>
@@ -6392,7 +6389,7 @@
         <v>0</v>
       </c>
       <c r="B280" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C280">
         <v>200000000</v>
@@ -6413,7 +6410,7 @@
         <v>0</v>
       </c>
       <c r="B281" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C281">
         <v>200000000</v>
@@ -6707,7 +6704,7 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C295">
         <v>250000000</v>
@@ -6728,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C296">
         <v>200000000</v>
@@ -6749,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C297">
         <v>200000000</v>
@@ -6770,7 +6767,7 @@
         <v>2</v>
       </c>
       <c r="B298" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C298">
         <v>150000000</v>
@@ -6791,7 +6788,7 @@
         <v>2</v>
       </c>
       <c r="B299" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C299">
         <v>100000000</v>
@@ -6812,7 +6809,7 @@
         <v>2</v>
       </c>
       <c r="B300" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C300">
         <v>170000000</v>
@@ -6833,7 +6830,7 @@
         <v>2</v>
       </c>
       <c r="B301" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C301">
         <v>75000000</v>
@@ -6854,7 +6851,7 @@
         <v>2</v>
       </c>
       <c r="B302" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C302">
         <v>100000000</v>
@@ -6875,7 +6872,7 @@
         <v>2</v>
       </c>
       <c r="B303" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C303">
         <v>85000000</v>
@@ -6896,7 +6893,7 @@
         <v>2</v>
       </c>
       <c r="B304" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C304">
         <v>4350000000</v>
@@ -6917,7 +6914,7 @@
         <v>2</v>
       </c>
       <c r="B305" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C305">
         <v>4900000000</v>
@@ -6938,7 +6935,7 @@
         <v>2</v>
       </c>
       <c r="B306" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C306">
         <v>3930000000</v>
@@ -6959,7 +6956,7 @@
         <v>2</v>
       </c>
       <c r="B307" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C307">
         <v>2925000000</v>
@@ -6980,7 +6977,7 @@
         <v>2</v>
       </c>
       <c r="B308" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C308">
         <v>2900000000</v>
@@ -7001,7 +6998,7 @@
         <v>2</v>
       </c>
       <c r="B309" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C309">
         <v>2815000000</v>
@@ -7022,7 +7019,7 @@
         <v>3</v>
       </c>
       <c r="B310" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C310">
         <v>500000000</v>
@@ -7043,7 +7040,7 @@
         <v>3</v>
       </c>
       <c r="B311" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C311">
         <v>300000000</v>
@@ -7064,7 +7061,7 @@
         <v>3</v>
       </c>
       <c r="B312" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C312">
         <v>200000000</v>
@@ -7085,7 +7082,7 @@
         <v>4</v>
       </c>
       <c r="B313" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C313">
         <v>800000000</v>
@@ -7106,7 +7103,7 @@
         <v>4</v>
       </c>
       <c r="B314" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C314">
         <v>1500000000</v>
@@ -7127,7 +7124,7 @@
         <v>4</v>
       </c>
       <c r="B315" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C315">
         <v>2000000000</v>
@@ -7211,7 +7208,7 @@
         <v>0</v>
       </c>
       <c r="B319" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C319" s="1">
         <v>200000000</v>
@@ -7232,7 +7229,7 @@
         <v>0</v>
       </c>
       <c r="B320" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C320" s="1">
         <v>200000000</v>
@@ -7253,7 +7250,7 @@
         <v>2</v>
       </c>
       <c r="B321" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C321">
         <v>3125000000</v>
@@ -7274,7 +7271,7 @@
         <v>2</v>
       </c>
       <c r="B322" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C322">
         <v>2187500000</v>
@@ -7295,7 +7292,7 @@
         <v>2</v>
       </c>
       <c r="B323" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C323">
         <v>3125000000</v>
@@ -7316,7 +7313,7 @@
         <v>2</v>
       </c>
       <c r="B324" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C324">
         <v>2812500000</v>
@@ -7337,7 +7334,7 @@
         <v>2</v>
       </c>
       <c r="B325" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C325">
         <v>3125000000</v>
@@ -7358,7 +7355,7 @@
         <v>2</v>
       </c>
       <c r="B326" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C326">
         <v>3125000000</v>
@@ -7379,7 +7376,7 @@
         <v>2</v>
       </c>
       <c r="B327" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C327">
         <v>5000000000</v>
@@ -7400,7 +7397,7 @@
         <v>2</v>
       </c>
       <c r="B328" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C328">
         <v>8125000000</v>
@@ -7421,7 +7418,7 @@
         <v>2</v>
       </c>
       <c r="B329" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C329">
         <v>5000000000</v>
@@ -7442,7 +7439,7 @@
         <v>2</v>
       </c>
       <c r="B330" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C330">
         <v>4375000000</v>
@@ -7463,7 +7460,7 @@
         <v>2</v>
       </c>
       <c r="B331" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C331">
         <v>5625000000</v>
@@ -7484,7 +7481,7 @@
         <v>2</v>
       </c>
       <c r="B332" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C332">
         <v>4375000000</v>
@@ -7505,7 +7502,7 @@
         <v>2</v>
       </c>
       <c r="B333" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C333">
         <v>1750000000</v>
@@ -7526,7 +7523,7 @@
         <v>2</v>
       </c>
       <c r="B334" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C334">
         <v>1225000000</v>
@@ -7547,7 +7544,7 @@
         <v>2</v>
       </c>
       <c r="B335" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C335">
         <v>1750000000</v>
@@ -7568,7 +7565,7 @@
         <v>2</v>
       </c>
       <c r="B336" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C336">
         <v>1575000000</v>
@@ -7589,7 +7586,7 @@
         <v>2</v>
       </c>
       <c r="B337" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C337">
         <v>1750000000</v>
@@ -7610,7 +7607,7 @@
         <v>2</v>
       </c>
       <c r="B338" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C338">
         <v>1750000000</v>
@@ -7631,7 +7628,7 @@
         <v>2</v>
       </c>
       <c r="B339" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C339">
         <v>2800000000</v>
@@ -7652,7 +7649,7 @@
         <v>2</v>
       </c>
       <c r="B340" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C340">
         <v>4550000000</v>
@@ -7673,7 +7670,7 @@
         <v>2</v>
       </c>
       <c r="B341" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C341">
         <v>2800000000</v>
@@ -7694,7 +7691,7 @@
         <v>2</v>
       </c>
       <c r="B342" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C342">
         <v>2450000000</v>
@@ -7715,7 +7712,7 @@
         <v>2</v>
       </c>
       <c r="B343" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C343">
         <v>3150000000</v>
@@ -7736,7 +7733,7 @@
         <v>2</v>
       </c>
       <c r="B344" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C344">
         <v>2450000000</v>
@@ -7757,7 +7754,7 @@
         <v>2</v>
       </c>
       <c r="B345" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C345">
         <v>75000000</v>
@@ -7778,7 +7775,7 @@
         <v>2</v>
       </c>
       <c r="B346" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C346">
         <v>52500000</v>
@@ -7799,7 +7796,7 @@
         <v>2</v>
       </c>
       <c r="B347" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C347">
         <v>75000000</v>
@@ -7820,7 +7817,7 @@
         <v>2</v>
       </c>
       <c r="B348" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C348">
         <v>67500000</v>
@@ -7841,7 +7838,7 @@
         <v>2</v>
       </c>
       <c r="B349" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C349">
         <v>75000000</v>
@@ -7862,7 +7859,7 @@
         <v>2</v>
       </c>
       <c r="B350" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C350">
         <v>75000000</v>
@@ -7883,7 +7880,7 @@
         <v>2</v>
       </c>
       <c r="B351" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C351">
         <v>120000000</v>
@@ -7904,7 +7901,7 @@
         <v>2</v>
       </c>
       <c r="B352" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C352">
         <v>195000000</v>
@@ -7925,7 +7922,7 @@
         <v>2</v>
       </c>
       <c r="B353" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C353">
         <v>120000000</v>
@@ -7946,7 +7943,7 @@
         <v>2</v>
       </c>
       <c r="B354" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C354">
         <v>105000000</v>
@@ -7967,7 +7964,7 @@
         <v>2</v>
       </c>
       <c r="B355" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C355">
         <v>135000000</v>
@@ -7988,7 +7985,7 @@
         <v>2</v>
       </c>
       <c r="B356" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C356">
         <v>105000000</v>
@@ -8009,7 +8006,7 @@
         <v>2</v>
       </c>
       <c r="B357" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C357">
         <v>50000000</v>
@@ -8030,7 +8027,7 @@
         <v>2</v>
       </c>
       <c r="B358" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C358">
         <v>35000000</v>
@@ -8051,7 +8048,7 @@
         <v>2</v>
       </c>
       <c r="B359" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C359">
         <v>50000000</v>
@@ -8072,7 +8069,7 @@
         <v>2</v>
       </c>
       <c r="B360" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C360">
         <v>45000000</v>
@@ -8093,7 +8090,7 @@
         <v>2</v>
       </c>
       <c r="B361" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C361">
         <v>50000000</v>
@@ -8114,7 +8111,7 @@
         <v>2</v>
       </c>
       <c r="B362" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C362">
         <v>50000000</v>
@@ -8135,7 +8132,7 @@
         <v>2</v>
       </c>
       <c r="B363" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C363">
         <v>80000000</v>
@@ -8156,7 +8153,7 @@
         <v>2</v>
       </c>
       <c r="B364" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C364">
         <v>130000000</v>
@@ -8177,7 +8174,7 @@
         <v>2</v>
       </c>
       <c r="B365" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C365">
         <v>80000000</v>
@@ -8198,7 +8195,7 @@
         <v>2</v>
       </c>
       <c r="B366" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C366">
         <v>70000000</v>
@@ -8219,7 +8216,7 @@
         <v>2</v>
       </c>
       <c r="B367" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C367">
         <v>90000000</v>
@@ -8240,7 +8237,7 @@
         <v>2</v>
       </c>
       <c r="B368" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C368">
         <v>70000000</v>
@@ -11285,7 +11282,7 @@
         <v>0</v>
       </c>
       <c r="B513" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C513">
         <v>200000000</v>
@@ -11306,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="B514" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C514">
         <v>200000000</v>
@@ -11327,10 +11324,10 @@
         <v>0</v>
       </c>
       <c r="B515" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C515">
-        <v>190000000</v>
+        <v>0</v>
       </c>
       <c r="D515" s="4">
         <v>3</v>
@@ -11348,10 +11345,10 @@
         <v>0</v>
       </c>
       <c r="B516" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C516">
-        <v>185000000</v>
+        <v>0</v>
       </c>
       <c r="D516" s="4">
         <v>4</v>
@@ -11369,7 +11366,7 @@
         <v>0</v>
       </c>
       <c r="B517" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C517">
         <v>190000000</v>
@@ -11390,7 +11387,7 @@
         <v>0</v>
       </c>
       <c r="B518" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C518">
         <v>200000000</v>
@@ -11411,7 +11408,7 @@
         <v>0</v>
       </c>
       <c r="B519" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C519">
         <v>190000000</v>
@@ -11432,7 +11429,7 @@
         <v>0</v>
       </c>
       <c r="B520" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C520">
         <v>330000000</v>
@@ -11453,7 +11450,7 @@
         <v>0</v>
       </c>
       <c r="B521" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C521">
         <v>195000000</v>
@@ -11474,7 +11471,7 @@
         <v>0</v>
       </c>
       <c r="B522" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C522">
         <v>160000000</v>
@@ -11495,7 +11492,7 @@
         <v>0</v>
       </c>
       <c r="B523" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C523">
         <v>220000000</v>
@@ -11516,7 +11513,7 @@
         <v>0</v>
       </c>
       <c r="B524" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C524">
         <v>170000000</v>
@@ -11789,7 +11786,7 @@
         <v>0</v>
       </c>
       <c r="B537" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C537">
         <v>240000000</v>
@@ -11810,7 +11807,7 @@
         <v>0</v>
       </c>
       <c r="B538" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C538">
         <v>240000000</v>
@@ -11831,7 +11828,7 @@
         <v>0</v>
       </c>
       <c r="B539" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C539">
         <v>200000000</v>
@@ -11852,7 +11849,7 @@
         <v>0</v>
       </c>
       <c r="B540" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C540">
         <v>220000000</v>
@@ -11864,7 +11861,7 @@
         <v>2026</v>
       </c>
       <c r="F540" s="3">
-        <f t="shared" ref="F540:F595" si="10">DATE(E540,D540,1)</f>
+        <f t="shared" ref="F540:F596" si="10">DATE(E540,D540,1)</f>
         <v>46023</v>
       </c>
     </row>
@@ -11873,7 +11870,7 @@
         <v>0</v>
       </c>
       <c r="B541" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C541">
         <v>210000000</v>
@@ -11894,7 +11891,7 @@
         <v>0</v>
       </c>
       <c r="B542" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C542">
         <v>220000000</v>
@@ -11915,7 +11912,7 @@
         <v>0</v>
       </c>
       <c r="B543" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C543">
         <v>210000000</v>
@@ -11936,7 +11933,7 @@
         <v>0</v>
       </c>
       <c r="B544" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C544">
         <v>180000000</v>
@@ -11957,7 +11954,7 @@
         <v>0</v>
       </c>
       <c r="B545" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C545">
         <v>200000000</v>
@@ -11978,7 +11975,7 @@
         <v>0</v>
       </c>
       <c r="B546" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C546">
         <v>200000000</v>
@@ -11999,7 +11996,7 @@
         <v>0</v>
       </c>
       <c r="B547" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C547">
         <v>250000000</v>
@@ -12020,7 +12017,7 @@
         <v>0</v>
       </c>
       <c r="B548" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C548">
         <v>290000000</v>
@@ -12041,7 +12038,7 @@
         <v>0</v>
       </c>
       <c r="B549" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C549">
         <v>200000000</v>
@@ -12062,7 +12059,7 @@
         <v>0</v>
       </c>
       <c r="B550" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C550">
         <v>190000000</v>
@@ -12083,7 +12080,7 @@
         <v>0</v>
       </c>
       <c r="B551" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C551">
         <v>260000000</v>
@@ -12104,7 +12101,7 @@
         <v>0</v>
       </c>
       <c r="B552" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C552">
         <v>200000000</v>
@@ -12125,20 +12122,20 @@
         <v>0</v>
       </c>
       <c r="B553" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C553">
-        <v>180000000</v>
+        <v>200000000</v>
       </c>
       <c r="D553" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E553">
         <v>2026</v>
       </c>
       <c r="F553" s="3">
         <f t="shared" si="10"/>
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.35">
@@ -12146,20 +12143,20 @@
         <v>0</v>
       </c>
       <c r="B554" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C554">
         <v>200000000</v>
       </c>
       <c r="D554" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E554">
         <v>2026</v>
       </c>
       <c r="F554" s="3">
         <f t="shared" si="10"/>
-        <v>46143</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.35">
@@ -12167,20 +12164,20 @@
         <v>0</v>
       </c>
       <c r="B555" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C555">
-        <v>200000000</v>
+        <v>250000000</v>
       </c>
       <c r="D555" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E555">
         <v>2026</v>
       </c>
       <c r="F555" s="3">
         <f t="shared" si="10"/>
-        <v>46174</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.35">
@@ -12188,20 +12185,20 @@
         <v>0</v>
       </c>
       <c r="B556" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C556">
-        <v>250000000</v>
+        <v>290000000</v>
       </c>
       <c r="D556" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E556">
         <v>2026</v>
       </c>
       <c r="F556" s="3">
         <f t="shared" si="10"/>
-        <v>46204</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.35">
@@ -12209,20 +12206,20 @@
         <v>0</v>
       </c>
       <c r="B557" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C557">
-        <v>290000000</v>
+        <v>200000000</v>
       </c>
       <c r="D557" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E557">
         <v>2026</v>
       </c>
       <c r="F557" s="3">
         <f t="shared" si="10"/>
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.35">
@@ -12230,20 +12227,20 @@
         <v>0</v>
       </c>
       <c r="B558" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C558">
-        <v>200000000</v>
+        <v>190000000</v>
       </c>
       <c r="D558" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E558">
         <v>2026</v>
       </c>
       <c r="F558" s="3">
         <f t="shared" si="10"/>
-        <v>46266</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.35">
@@ -12251,20 +12248,20 @@
         <v>0</v>
       </c>
       <c r="B559" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C559">
-        <v>190000000</v>
+        <v>260000000</v>
       </c>
       <c r="D559" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E559">
         <v>2026</v>
       </c>
       <c r="F559" s="3">
         <f t="shared" si="10"/>
-        <v>46296</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.35">
@@ -12272,20 +12269,20 @@
         <v>0</v>
       </c>
       <c r="B560" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C560">
-        <v>260000000</v>
+        <v>200000000</v>
       </c>
       <c r="D560" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E560">
         <v>2026</v>
       </c>
       <c r="F560" s="3">
         <f t="shared" si="10"/>
-        <v>46327</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.35">
@@ -12293,20 +12290,20 @@
         <v>0</v>
       </c>
       <c r="B561" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C561">
-        <v>200000000</v>
+        <v>180000000</v>
       </c>
       <c r="D561" s="4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E561">
         <v>2026</v>
       </c>
       <c r="F561" s="3">
         <f t="shared" si="10"/>
-        <v>46357</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.35">
@@ -12314,20 +12311,20 @@
         <v>0</v>
       </c>
       <c r="B562" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C562">
-        <v>180000000</v>
+        <v>200000000</v>
       </c>
       <c r="D562" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E562">
         <v>2026</v>
       </c>
       <c r="F562" s="3">
         <f t="shared" si="10"/>
-        <v>46143</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.35">
@@ -12335,20 +12332,20 @@
         <v>0</v>
       </c>
       <c r="B563" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C563">
-        <v>200000000</v>
+        <v>250000000</v>
       </c>
       <c r="D563" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E563">
         <v>2026</v>
       </c>
       <c r="F563" s="3">
         <f t="shared" si="10"/>
-        <v>46174</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.35">
@@ -12356,20 +12353,20 @@
         <v>0</v>
       </c>
       <c r="B564" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C564">
-        <v>250000000</v>
+        <v>290000000</v>
       </c>
       <c r="D564" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E564">
         <v>2026</v>
       </c>
       <c r="F564" s="3">
         <f t="shared" si="10"/>
-        <v>46204</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.35">
@@ -12377,20 +12374,20 @@
         <v>0</v>
       </c>
       <c r="B565" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C565">
-        <v>290000000</v>
+        <v>200000000</v>
       </c>
       <c r="D565" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E565">
         <v>2026</v>
       </c>
       <c r="F565" s="3">
         <f t="shared" si="10"/>
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.35">
@@ -12398,20 +12395,20 @@
         <v>0</v>
       </c>
       <c r="B566" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C566">
-        <v>200000000</v>
+        <v>190000000</v>
       </c>
       <c r="D566" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E566">
         <v>2026</v>
       </c>
       <c r="F566" s="3">
         <f t="shared" si="10"/>
-        <v>46266</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.35">
@@ -12419,20 +12416,20 @@
         <v>0</v>
       </c>
       <c r="B567" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C567">
-        <v>190000000</v>
+        <v>260000000</v>
       </c>
       <c r="D567" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E567">
         <v>2026</v>
       </c>
       <c r="F567" s="3">
         <f t="shared" si="10"/>
-        <v>46296</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.35">
@@ -12440,20 +12437,20 @@
         <v>0</v>
       </c>
       <c r="B568" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C568">
-        <v>260000000</v>
+        <v>200000000</v>
       </c>
       <c r="D568" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E568">
         <v>2026</v>
       </c>
       <c r="F568" s="3">
         <f t="shared" si="10"/>
-        <v>46327</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.35">
@@ -12461,20 +12458,20 @@
         <v>0</v>
       </c>
       <c r="B569" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C569">
-        <v>200000000</v>
+        <v>180000000</v>
       </c>
       <c r="D569" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E569">
         <v>2026</v>
       </c>
       <c r="F569" s="3">
         <f t="shared" si="10"/>
-        <v>46357</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.35">
@@ -12482,20 +12479,20 @@
         <v>0</v>
       </c>
       <c r="B570" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C570">
-        <v>180000000</v>
+        <v>200000000</v>
       </c>
       <c r="D570" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E570">
         <v>2026</v>
       </c>
       <c r="F570" s="3">
         <f t="shared" si="10"/>
-        <v>46174</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.35">
@@ -12503,20 +12500,20 @@
         <v>0</v>
       </c>
       <c r="B571" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C571">
-        <v>200000000</v>
+        <v>260000000</v>
       </c>
       <c r="D571" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E571">
         <v>2026</v>
       </c>
       <c r="F571" s="3">
         <f t="shared" si="10"/>
-        <v>46204</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.35">
@@ -12524,20 +12521,20 @@
         <v>0</v>
       </c>
       <c r="B572" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C572">
-        <v>260000000</v>
+        <v>200000000</v>
       </c>
       <c r="D572" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E572">
         <v>2026</v>
       </c>
       <c r="F572" s="3">
         <f t="shared" si="10"/>
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.35">
@@ -12545,20 +12542,20 @@
         <v>0</v>
       </c>
       <c r="B573" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C573">
-        <v>200000000</v>
+        <v>190000000</v>
       </c>
       <c r="D573" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E573">
         <v>2026</v>
       </c>
       <c r="F573" s="3">
         <f t="shared" si="10"/>
-        <v>46266</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.35">
@@ -12566,20 +12563,20 @@
         <v>0</v>
       </c>
       <c r="B574" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C574">
-        <v>190000000</v>
+        <v>260000000</v>
       </c>
       <c r="D574" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E574">
         <v>2026</v>
       </c>
       <c r="F574" s="3">
         <f t="shared" si="10"/>
-        <v>46296</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.35">
@@ -12587,20 +12584,20 @@
         <v>0</v>
       </c>
       <c r="B575" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C575">
-        <v>260000000</v>
+        <v>200000000</v>
       </c>
       <c r="D575" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E575">
         <v>2026</v>
       </c>
       <c r="F575" s="3">
         <f t="shared" si="10"/>
-        <v>46327</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.35">
@@ -12608,20 +12605,20 @@
         <v>0</v>
       </c>
       <c r="B576" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C576">
-        <v>200000000</v>
+        <v>180000000</v>
       </c>
       <c r="D576" s="4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E576">
         <v>2026</v>
       </c>
       <c r="F576" s="3">
         <f t="shared" si="10"/>
-        <v>46357</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.35">
@@ -12629,20 +12626,20 @@
         <v>0</v>
       </c>
       <c r="B577" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C577">
-        <v>180000000</v>
+        <v>190000000</v>
       </c>
       <c r="D577" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E577">
         <v>2026</v>
       </c>
       <c r="F577" s="3">
         <f t="shared" si="10"/>
-        <v>46266</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.35">
@@ -12650,20 +12647,20 @@
         <v>0</v>
       </c>
       <c r="B578" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C578">
-        <v>190000000</v>
+        <v>240000000</v>
       </c>
       <c r="D578" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E578">
         <v>2026</v>
       </c>
       <c r="F578" s="3">
         <f t="shared" si="10"/>
-        <v>46296</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.35">
@@ -12671,20 +12668,20 @@
         <v>0</v>
       </c>
       <c r="B579" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C579">
-        <v>240000000</v>
+        <v>200000000</v>
       </c>
       <c r="D579" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E579">
         <v>2026</v>
       </c>
       <c r="F579" s="3">
         <f t="shared" si="10"/>
-        <v>46327</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.35">
@@ -12692,20 +12689,20 @@
         <v>0</v>
       </c>
       <c r="B580" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C580">
-        <v>200000000</v>
+        <v>180000000</v>
       </c>
       <c r="D580" s="4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E580">
         <v>2026</v>
       </c>
       <c r="F580" s="3">
         <f t="shared" si="10"/>
-        <v>46357</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.35">
@@ -12713,20 +12710,20 @@
         <v>0</v>
       </c>
       <c r="B581" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C581">
-        <v>180000000</v>
+        <v>220000000</v>
       </c>
       <c r="D581" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E581">
         <v>2026</v>
       </c>
       <c r="F581" s="3">
         <f t="shared" si="10"/>
-        <v>46296</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.35">
@@ -12734,41 +12731,41 @@
         <v>0</v>
       </c>
       <c r="B582" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C582">
-        <v>220000000</v>
+        <v>200000000</v>
       </c>
       <c r="D582" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E582">
         <v>2026</v>
       </c>
       <c r="F582" s="3">
         <f t="shared" si="10"/>
-        <v>46327</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B583" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="C583">
-        <v>200000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D583" s="4">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E583">
         <v>2026</v>
       </c>
       <c r="F583" s="3">
         <f t="shared" si="10"/>
-        <v>46357</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.35">
@@ -12779,17 +12776,17 @@
         <v>1</v>
       </c>
       <c r="C584">
-        <v>2500000000</v>
+        <v>1300000000</v>
       </c>
       <c r="D584" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E584">
         <v>2026</v>
       </c>
       <c r="F584" s="3">
         <f t="shared" si="10"/>
-        <v>46023</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.35">
@@ -12800,17 +12797,17 @@
         <v>1</v>
       </c>
       <c r="C585">
-        <v>1300000000</v>
+        <v>1800000000</v>
       </c>
       <c r="D585" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E585">
         <v>2026</v>
       </c>
       <c r="F585" s="3">
         <f t="shared" si="10"/>
-        <v>46054</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.35">
@@ -12824,14 +12821,14 @@
         <v>1800000000</v>
       </c>
       <c r="D586" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E586">
         <v>2026</v>
       </c>
       <c r="F586" s="3">
         <f t="shared" si="10"/>
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.35">
@@ -12842,17 +12839,17 @@
         <v>1</v>
       </c>
       <c r="C587">
-        <v>1800000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D587" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E587">
         <v>2026</v>
       </c>
       <c r="F587" s="3">
         <f t="shared" si="10"/>
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.35">
@@ -12863,17 +12860,17 @@
         <v>1</v>
       </c>
       <c r="C588">
-        <v>1900000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D588" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E588">
         <v>2026</v>
       </c>
       <c r="F588" s="3">
         <f t="shared" si="10"/>
-        <v>46143</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.35">
@@ -12884,17 +12881,17 @@
         <v>1</v>
       </c>
       <c r="C589">
-        <v>2000000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D589" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E589">
         <v>2026</v>
       </c>
       <c r="F589" s="3">
         <f t="shared" si="10"/>
-        <v>46174</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.35">
@@ -12905,17 +12902,17 @@
         <v>1</v>
       </c>
       <c r="C590">
-        <v>2900000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D590" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E590">
         <v>2026</v>
       </c>
       <c r="F590" s="3">
         <f t="shared" si="10"/>
-        <v>46204</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.35">
@@ -12926,17 +12923,17 @@
         <v>1</v>
       </c>
       <c r="C591">
-        <v>4500000000</v>
+        <v>2700000000</v>
       </c>
       <c r="D591" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E591">
         <v>2026</v>
       </c>
       <c r="F591" s="3">
         <f t="shared" si="10"/>
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.35">
@@ -12947,17 +12944,17 @@
         <v>1</v>
       </c>
       <c r="C592">
-        <v>2700000000</v>
+        <v>2300000000</v>
       </c>
       <c r="D592" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E592">
         <v>2026</v>
       </c>
       <c r="F592" s="3">
         <f t="shared" si="10"/>
-        <v>46266</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.35">
@@ -12971,14 +12968,14 @@
         <v>2300000000</v>
       </c>
       <c r="D593" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E593">
         <v>2026</v>
       </c>
       <c r="F593" s="3">
         <f t="shared" si="10"/>
-        <v>46296</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.35">
@@ -12989,38 +12986,59 @@
         <v>1</v>
       </c>
       <c r="C594">
-        <v>2300000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D594" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E594">
         <v>2026</v>
       </c>
       <c r="F594" s="3">
         <f t="shared" si="10"/>
-        <v>46327</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B595" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C595">
-        <v>2000000000</v>
-      </c>
-      <c r="D595" s="4">
-        <v>12</v>
+        <v>180000000</v>
+      </c>
+      <c r="D595">
+        <v>3</v>
       </c>
       <c r="E595">
         <v>2026</v>
       </c>
       <c r="F595" s="3">
         <f t="shared" si="10"/>
-        <v>46357</v>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="596" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A596" t="s">
+        <v>0</v>
+      </c>
+      <c r="B596" t="s">
+        <v>18</v>
+      </c>
+      <c r="C596">
+        <v>180000000</v>
+      </c>
+      <c r="D596">
+        <v>4</v>
+      </c>
+      <c r="E596">
+        <v>2026</v>
+      </c>
+      <c r="F596" s="3">
+        <f t="shared" si="10"/>
+        <v>46113</v>
       </c>
     </row>
   </sheetData>
